--- a/记录人生/01游戏攻略/异度之刃/ゼノブレイドDE_任务管理..xlsx
+++ b/记录人生/01游戏攻略/异度之刃/ゼノブレイドDE_任务管理..xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25590" windowHeight="12800" firstSheet="14" activeTab="19"/>
+    <workbookView windowWidth="25590" windowHeight="12800" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="ゼノブレイドDE_任务管理" sheetId="12" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1693" uniqueCount="695">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1695" uniqueCount="695">
   <si>
     <t>汇总一览</t>
   </si>
@@ -3780,7 +3780,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3825,6 +3825,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -4722,20 +4725,20 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="17" t="str">
+      <c r="B2" s="18" t="str">
         <f t="shared" ref="B2:B18" si="0">HYPERLINK("#'"&amp;A2&amp;"'!A1",A2)</f>
         <v>コロニー9-任務</v>
       </c>
       <c r="C2" s="14">
         <f ca="1" t="shared" ref="C2:C18" si="1">INDIRECT("'"&amp;A2&amp;"'!B2")</f>
-        <v>74</v>
-      </c>
-      <c r="D2" s="18">
+        <v>79</v>
+      </c>
+      <c r="D2" s="19">
         <f ca="1" t="shared" ref="D2:D18" si="2">INDIRECT("'"&amp;B2&amp;"'!B4")</f>
-        <v>0.91358024691358</v>
+        <v>0.975308641975309</v>
       </c>
       <c r="E2" s="14">
         <f ca="1" t="shared" ref="E2:E18" si="3">INDIRECT("'"&amp;A2&amp;"'!B3")+INDIRECT("'"&amp;A2&amp;"'!B2")</f>
@@ -4746,7 +4749,7 @@
       <c r="A3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="17" t="str">
+      <c r="B3" s="18" t="str">
         <f t="shared" si="0"/>
         <v>テフラ洞窟-任務</v>
       </c>
@@ -4754,7 +4757,7 @@
         <f ca="1" t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="D3" s="18">
+      <c r="D3" s="19">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -4767,17 +4770,17 @@
       <c r="A4" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="19" t="str">
+      <c r="B4" s="20" t="str">
         <f t="shared" si="0"/>
         <v>巨神脚-任務</v>
       </c>
       <c r="C4" s="14">
         <f ca="1" t="shared" si="1"/>
-        <v>35</v>
-      </c>
-      <c r="D4" s="18">
+        <v>36</v>
+      </c>
+      <c r="D4" s="19">
         <f ca="1" t="shared" si="2"/>
-        <v>0.921052631578947</v>
+        <v>0.947368421052632</v>
       </c>
       <c r="E4" s="14">
         <f ca="1" t="shared" si="3"/>
@@ -4788,7 +4791,7 @@
       <c r="A5" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="19" t="str">
+      <c r="B5" s="20" t="str">
         <f t="shared" si="0"/>
         <v>コロニー6-任務</v>
       </c>
@@ -4796,7 +4799,7 @@
         <f ca="1" t="shared" si="1"/>
         <v>33</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="19">
         <f ca="1" t="shared" si="2"/>
         <v>0.492537313432836</v>
       </c>
@@ -4809,7 +4812,7 @@
       <c r="A6" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="19" t="str">
+      <c r="B6" s="20" t="str">
         <f t="shared" si="0"/>
         <v>燐光の地ザトール-任務</v>
       </c>
@@ -4817,7 +4820,7 @@
         <f ca="1" t="shared" si="1"/>
         <v>23</v>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="19">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -4830,7 +4833,7 @@
       <c r="A7" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="17" t="str">
+      <c r="B7" s="18" t="str">
         <f t="shared" si="0"/>
         <v>マクナ原生林-任務</v>
       </c>
@@ -4838,7 +4841,7 @@
         <f ca="1" t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="19">
         <f ca="1" t="shared" si="2"/>
         <v>0.9</v>
       </c>
@@ -4851,7 +4854,7 @@
       <c r="A8" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="17" t="str">
+      <c r="B8" s="18" t="str">
         <f t="shared" si="0"/>
         <v>サイハテ村-任務</v>
       </c>
@@ -4859,7 +4862,7 @@
         <f ca="1" t="shared" si="1"/>
         <v>77</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="19">
         <f ca="1" t="shared" si="2"/>
         <v>0.916666666666667</v>
       </c>
@@ -4872,7 +4875,7 @@
       <c r="A9" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="19" t="str">
+      <c r="B9" s="20" t="str">
         <f t="shared" si="0"/>
         <v>エルト海-任務</v>
       </c>
@@ -4880,7 +4883,7 @@
         <f ca="1" t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="19">
         <f ca="1" t="shared" si="2"/>
         <v>0.789473684210526</v>
       </c>
@@ -4893,7 +4896,7 @@
       <c r="A10" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="17" t="str">
+      <c r="B10" s="18" t="str">
         <f t="shared" si="0"/>
         <v>皇都アカモート-任務</v>
       </c>
@@ -4901,7 +4904,7 @@
         <f ca="1" t="shared" si="1"/>
         <v>56</v>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="19">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -4914,7 +4917,7 @@
       <c r="A11" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="17" t="str">
+      <c r="B11" s="18" t="str">
         <f t="shared" si="0"/>
         <v>ヴァラク雪山-任務</v>
       </c>
@@ -4922,7 +4925,7 @@
         <f ca="1" t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="19">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -4935,7 +4938,7 @@
       <c r="A12" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="17" t="str">
+      <c r="B12" s="18" t="str">
         <f t="shared" si="0"/>
         <v>大剣の渓谷-任務</v>
       </c>
@@ -4943,7 +4946,7 @@
         <f ca="1" t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="19">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -4956,7 +4959,7 @@
       <c r="A13" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="17" t="str">
+      <c r="B13" s="18" t="str">
         <f t="shared" si="0"/>
         <v>ガラハド要塞-任務</v>
       </c>
@@ -4964,7 +4967,7 @@
         <f ca="1" t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="19">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -4977,7 +4980,7 @@
       <c r="A14" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="19" t="str">
+      <c r="B14" s="20" t="str">
         <f t="shared" si="0"/>
         <v>落ちた腕-任務</v>
       </c>
@@ -4985,7 +4988,7 @@
         <f ca="1" t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="D14" s="18">
+      <c r="D14" s="19">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -4998,7 +5001,7 @@
       <c r="A15" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="17" t="str">
+      <c r="B15" s="18" t="str">
         <f t="shared" si="0"/>
         <v>機神界フィールド-任務</v>
       </c>
@@ -5006,7 +5009,7 @@
         <f ca="1" t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="D15" s="18">
+      <c r="D15" s="19">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -5019,7 +5022,7 @@
       <c r="A16" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="17" t="str">
+      <c r="B16" s="18" t="str">
         <f t="shared" si="0"/>
         <v>中央工廠-任務</v>
       </c>
@@ -5027,7 +5030,7 @@
         <f ca="1" t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="D16" s="18">
+      <c r="D16" s="19">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -5040,7 +5043,7 @@
       <c r="A17" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="19" t="str">
+      <c r="B17" s="20" t="str">
         <f t="shared" si="0"/>
         <v>帝都アグニラータ-任務</v>
       </c>
@@ -5048,7 +5051,7 @@
         <f ca="1" t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="D17" s="18">
+      <c r="D17" s="19">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -5061,7 +5064,7 @@
       <c r="A18" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="17" t="str">
+      <c r="B18" s="18" t="str">
         <f t="shared" si="0"/>
         <v>監獄島(2回目)-任務</v>
       </c>
@@ -5069,7 +5072,7 @@
         <f ca="1" t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D18" s="18">
+      <c r="D18" s="19">
         <f ca="1" t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5080,14 +5083,14 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="14"/>
-      <c r="B19" s="20"/>
+      <c r="B19" s="21"/>
       <c r="C19" s="14">
         <f ca="1">SUBTOTAL(109,表_ゼノブレイドDE_任务管理__xlsx[已完成任务])</f>
-        <v>243</v>
-      </c>
-      <c r="D19" s="21">
+        <v>249</v>
+      </c>
+      <c r="D19" s="22">
         <f ca="1">表_ゼノブレイドDE_任务管理__xlsx[[#Totals],[已完成任务]]/表_ゼノブレイドDE_任务管理__xlsx[[#Totals],[总数]]</f>
-        <v>0.807308970099668</v>
+        <v>0.827242524916943</v>
       </c>
       <c r="E19">
         <f ca="1">SUBTOTAL(109,表_ゼノブレイドDE_任务管理__xlsx[总数])</f>
@@ -7916,7 +7919,7 @@
       <c r="A1" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="15"/>
+      <c r="B1" s="16"/>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
@@ -7924,7 +7927,7 @@
       </c>
       <c r="B2">
         <f>COUNTIF(表1[完成情况],"〇")</f>
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7933,7 +7936,7 @@
       </c>
       <c r="B3">
         <f>COUNTIF(表1[完成情况],"✕")</f>
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7942,7 +7945,7 @@
       </c>
       <c r="B4" s="3">
         <f>B2/MAX(表1[编号])</f>
-        <v>0.91358024691358</v>
+        <v>0.975308641975309</v>
       </c>
     </row>
     <row r="5" s="14" customFormat="1" spans="1:3">
@@ -7952,7 +7955,7 @@
       <c r="B5" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="17" t="s">
         <v>44</v>
       </c>
     </row>
@@ -8404,7 +8407,7 @@
         <v>87</v>
       </c>
       <c r="C46" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -8415,7 +8418,7 @@
         <v>88</v>
       </c>
       <c r="C47" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -8426,7 +8429,7 @@
         <v>89</v>
       </c>
       <c r="C48" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -8437,7 +8440,7 @@
         <v>90</v>
       </c>
       <c r="C49" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -8459,7 +8462,7 @@
         <v>92</v>
       </c>
       <c r="C51" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
     </row>
     <row r="52" hidden="1" spans="1:3">
@@ -8852,7 +8855,7 @@
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6:C1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6:C45 C46:C47 C48:C49 C50:C51 C52:C1048576">
       <formula1>"〇,✕"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8892,7 +8895,7 @@
       </c>
       <c r="B2">
         <f>COUNTIF(表16[完成情况],"〇")</f>
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -8901,7 +8904,7 @@
       </c>
       <c r="B3">
         <f>COUNTIF(表16[完成情况],"✕")+COUNTIF(表16[完成情况],"")</f>
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -8910,7 +8913,7 @@
       </c>
       <c r="B4" s="3">
         <f>B2/MAX(表16[编号])</f>
-        <v>0.719745222929936</v>
+        <v>0.732484076433121</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -9189,6 +9192,9 @@
       <c r="C24" t="s">
         <v>548</v>
       </c>
+      <c r="D24" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25">
@@ -9263,6 +9269,9 @@
       </c>
       <c r="C30" t="s">
         <v>554</v>
+      </c>
+      <c r="D30" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -10998,7 +11007,7 @@
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D6:D72 D73:D74 D75:D131 D132:D133 D134:D162">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D6:D22 D23:D24 D25:D28 D29:D30 D31:D72 D73:D74 D75:D131 D132:D133 D134:D162">
       <formula1>"〇,✕"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11246,10 +11255,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="6"/>
+      <c r="B1" s="9"/>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
@@ -11257,7 +11266,7 @@
       </c>
       <c r="B2">
         <f>COUNTIF(表4[完成情况],"〇")</f>
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -11266,7 +11275,7 @@
       </c>
       <c r="B3">
         <f>COUNTIF(表4[完成情况],"✕")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -11275,7 +11284,7 @@
       </c>
       <c r="B4" s="3">
         <f>B2/MAX(表4[编号])</f>
-        <v>0.921052631578947</v>
+        <v>0.947368421052632</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -11484,7 +11493,7 @@
         <v>158</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:3">
@@ -11712,7 +11721,7 @@
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6:C43">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6:C21 C22:C23 C24:C43">
       <formula1>"〇,✕"</formula1>
     </dataValidation>
   </dataValidations>
@@ -14505,11 +14514,11 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<DataMashup xmlns="http://schemas.microsoft.com/DataMashup">AAAAAAQFAABQSwMECgAAAAAAh07iQAAAAAAAAAAAAAAAAAcAAABDb25maWcvUEsDBBQAAAAIAIdO4kASOP6YnwAAAPMAAAASAAAAQ29uZmlnL1BhY2thZ2UueG1shY9NC4IwHMa/iuzuNmdRyN958JoRBNF1zDVHOsPNJn36jDK6dXtefofngWLq2uiuBmd6m6MEUxQpK/vaWJ2j0V/iLSo4HIS8Cq2iGbYum1ydo8b7W0ZICAGHFPeDJozShJyr3VE2qhPoC5v/cGys88JKhTic3mM4w8lqg9N1iimQJYTK2EUzzOa9r/YnhHJs/Tgo/mjicg9ksUA+H/gTUEsDBAoAAAAAAIdO4kAAAAAAAAAAAAAAAAAJAAAARm9ybXVsYXMvUEsDBBQAAAAIAIdO4kC93Sq2pgEAAO8DAAATAAAARm9ybXVsYXMvU2VjdGlvbjEubY2SbUvCQADH3wt+h2O9WXBISxNKetUDBeELDXozCK2DhnMLN0OIIFwP68Ey0KTe1KAnKKzeiG31abbb9Ft0ZZY4XR6M42D3+//ufyehFZkTBRBvzUzE7/P7pLVEBq2CIcrMv5vKiamcm8qTmb8xlYPpmWXLMPCh5lQ1p7gHQI6XchSYBDyS/T5Ahq0XyXImt4L4wJKYSSVFMUXPcjwKTImCjARZoqm5CdZ5KjWqLyz58EfZ0nWndMWOMHa9bqundslwyrcsfs9j/c56O8Kqwv6rEgh8qwxDIGR5HgI5k0XDsOWE1evmxY1zuYP1clN5aGjHRHExkSRSMZQWN9BCQpKjNFGH4+49aqXr7ymRz6YFiXZj4SYVTaQRteWmtJOZLlgr+g+lViDj3r1bs4xz3GESRzy5sv4mDFGZl1H6T6W5X8BnH7hY+OqhgxRDAlF2k9qRcPOHBAFlv+7b24ZV327cq9SW+5RNreY8Pnf2G09x63RXdK8DtusZ9a7nN8CLEfRm/D6CUS9IaEBI0AsyNiAkBJkel97uJDwgZYyo+H2c0O/RhyOfUEsDBBQAAAAIAIdO4kB/v9PKnQAAAOQAAAATAAAAW0NvbnRlbnRfVHlwZXNdLnhtbG2PSw7CMAxErxJ5n7qwQAg17aJwAy4QBfcjmo8aF4Xbk9AdYunxPM+46ZJdxIvWOHun4FDVIMgZ/5jdqGDjQZ6ha5v7O1AU2eqigok5XBCjmcjqWPlALm8Gv1rNeVxHDNo89Uh4rOsTGu+YHEsuN6BtrjTobWFxS1neYzMOot99JUoBU2IsMv4F7I9dh7DMRnN+ApO0UdoC4rd2+wFQSwECFAAUAAAACACHTuJAf7/Typ0AAADkAAAAEwAAAAAAAAABACAAAADyAgAAW0NvbnRlbnRfVHlwZXNdLnhtbFBLAQIUAAoAAAAAAIdO4kAAAAAAAAAAAAAAAAAHAAAAAAAAAAAAEAAAAAAAAABDb25maWcvUEsBAhQAFAAAAAgAh07iQBI4/pifAAAA8wAAABIAAAAAAAAAAQAgAAAAJQAAAENvbmZpZy9QYWNrYWdlLnhtbFBLAQIUAAoAAAAAAIdO4kAAAAAAAAAAAAAAAAAJAAAAAAAAAAAAEAAAAPQAAABGb3JtdWxhcy9QSwECFAAUAAAACACHTuJAvd0qtqYBAADvAwAAEwAAAAAAAAABACAAAAAbAQAARm9ybXVsYXMvU2VjdGlvbjEubVBLBQYAAAAABQAFAC4BAADAAwAAAAAOAQAAPD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXRmLTgiID8+PFBlcm1pc3Npb25MaXN0IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiPjxDYW5FdmFsdWF0ZUZ1dHVyZVBhY2thZ2VzPmZhbHNlPC9DYW5FdmFsdWF0ZUZ1dHVyZVBhY2thZ2VzPjxGaXJld2FsbEVuYWJsZWQ+dHJ1ZTwvRmlyZXdhbGxFbmFibGVkPjwvUGVybWlzc2lvbkxpc3Q+kwQAAAAAAABxBAAAPD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXRmLTgiID8+PExvY2FsUGFja2FnZU1ldGFkYXRhRmlsZSB4bWxuczp4c2Q9Imh0dHA6Ly93d3cudzMub3JnLzIwMDEvWE1MU2NoZW1hIiB4bWxuczp4c2k9Imh0dHA6Ly93d3cudzMub3JnLzIwMDEvWE1MU2NoZW1hLWluc3RhbmNlIj48SXRlbXM+PEl0ZW0+PEl0ZW1Mb2NhdGlvbj48SXRlbVR5cGU+QWxsRm9ybXVsYXM8L0l0ZW1UeXBlPjxJdGVtUGF0aCAvPjwvSXRlbUxvY2F0aW9uPjxTdGFibGVFbnRyaWVzPjxFbnRyeSBUeXBlPSJSZWxhdGlvbnNoaXBzIiBWYWx1ZT0ic0FBQUFBQT09IiAvPjwvU3RhYmxlRW50cmllcz48L0l0ZW0+PEl0ZW0+PEl0ZW1Mb2NhdGlvbj48SXRlbVR5cGU+Rm9ybXVsYTwvSXRlbVR5cGU+PEl0ZW1QYXRoPlNlY3Rpb24xLyVFMyU4MiVCQyVFMyU4MyU4RSVFMyU4MyU5NiVFMyU4MyVBQyVFMyU4MiVBNCVFMyU4MyU4OURFXyVFNCVCQiVCQiVFNSU4QSVBMSVFNyVBRSVBMSVFNyU5MCU4NiUyMCUyMHhsc3g8L0l0ZW1QYXRoPjwvSXRlbUxvY2F0aW9uPjxTdGFibGVFbnRyaWVzPjxFbnRyeSBUeXBlPSJJc1ByaXZhdGUiIFZhbHVlPSJsMCIgLz48RW50cnkgVHlwZT0iRmlsbEVuYWJsZWQiIFZhbHVlPSJsMSIgLz48RW50cnkgVHlwZT0iRmlsbE9iamVjdFR5cGUiIFZhbHVlPSJzVGFibGUiIC8+PEVudHJ5IFR5cGU9IlF1ZXJ5SUQiIFZhbHVlPSJzMzI0MDk1OTItMTBmMi00ZDk4LWI0OWQtNDlmNmQzYmIxMDAwIiAvPjxFbnRyeSBUeXBlPSJSZXN1bHRUeXBlIiBWYWx1ZT0ic1RhYmxlIiAvPjxFbnRyeSBUeXBlPSJGaWxsVGFyZ2V0IiBWYWx1ZT0ic+ihqF/jgrzjg47jg5bjg6zjgqTjg4lERV/ku7vliqHnrqHnkIZfX3hsc3giIC8+PEVudHJ5IFR5cGU9IkZpbGxDb3VudCIgVmFsdWU9ImwxNyIgLz48RW50cnkgVHlwZT0iRmlsbEVycm9yQ291bnQiIFZhbHVlPSJsMCIgLz48RW50cnkgVHlwZT0iRmlsbExhc3RVcGRhdGVkIiBWYWx1ZT0iZDIwMjYtMDUtMDZUMDU6MjE6MDMuNzY3MDAwMFoiIC8+PEVudHJ5IFR5cGU9IkZpbGxDb2x1bW5OYW1lcyIgVmFsdWU9J3NbJnF1b3Q75rGH5oC75LiA6KeIJnF1b3Q7XScgLz48L1N0YWJsZUVudHJpZXM+PC9JdGVtPjwvSXRlbXM+PC9Mb2NhbFBhY2thZ2VNZXRhZGF0YUZpbGU+FgAAAFBLBQYAAAAAAAAAAAAAAAAAAAAAAAAmAQAAAQAAANCMnd8BFdERjHoAwE/Cl+sBAAAA2cHvIhDB8U+DzvEXf4lk6wAAAAACAAAAAAAQZgAAAAEAACAAAAAg1tvjzb0prv4GZcfKYNw9X0S5Y6ljkWhrVpY0SSzvbgAAAAAOgAAAAAIAACAAAABhmmbkLC1A05bzBR0OzPhktlvwPb0rhMSCvyow1za3TFAAAAB4Hbo545uHI+VNR1Av4phfig21aUa2F25O3cCpWvPIhCuyRroZBfveLV0aX0r+lG+zaAwqRNaNT0PM+gwD5jLVG6C3sMSFJHe7F/8b3uAj+UAAAABg6RoLkcR4QAf8i/cFtnrKlHotX9bFq6BkJfDN07e4sbCM6edxcWXxPJ3kwBJhLSayibu3XdLFd1JMC9B3arxy</DataMashup>
+<DataMashup xmlns="http://schemas.microsoft.com/DataMashup">AAAAAAQFAABQSwMECgAAAAAAh07iQAAAAAAAAAAAAAAAAAcAAABDb25maWcvUEsDBBQAAAAIAIdO4kASOP6YnwAAAPMAAAASAAAAQ29uZmlnL1BhY2thZ2UueG1shY9NC4IwHMa/iuzuNmdRyN958JoRBNF1zDVHOsPNJn36jDK6dXtefofngWLq2uiuBmd6m6MEUxQpK/vaWJ2j0V/iLSo4HIS8Cq2iGbYum1ydo8b7W0ZICAGHFPeDJozShJyr3VE2qhPoC5v/cGys88JKhTic3mM4w8lqg9N1iimQJYTK2EUzzOa9r/YnhHJs/Tgo/mjicg9ksUA+H/gTUEsDBAoAAAAAAIdO4kAAAAAAAAAAAAAAAAAJAAAARm9ybXVsYXMvUEsDBBQAAAAIAIdO4kC93Sq2pgEAAO8DAAATAAAARm9ybXVsYXMvU2VjdGlvbjEubY2SbUvCQADH3wt+h2O9WXBISxNKetUDBeELDXozCK2DhnMLN0OIIFwP68Ey0KTe1KAnKKzeiG31abbb9Ft0ZZY4XR6M42D3+//ufyehFZkTBRBvzUzE7/P7pLVEBq2CIcrMv5vKiamcm8qTmb8xlYPpmWXLMPCh5lQ1p7gHQI6XchSYBDyS/T5Ahq0XyXImt4L4wJKYSSVFMUXPcjwKTImCjARZoqm5CdZ5KjWqLyz58EfZ0nWndMWOMHa9bqundslwyrcsfs9j/c56O8Kqwv6rEgh8qwxDIGR5HgI5k0XDsOWE1evmxY1zuYP1clN5aGjHRHExkSRSMZQWN9BCQpKjNFGH4+49aqXr7ymRz6YFiXZj4SYVTaQRteWmtJOZLlgr+g+lViDj3r1bs4xz3GESRzy5sv4mDFGZl1H6T6W5X8BnH7hY+OqhgxRDAlF2k9qRcPOHBAFlv+7b24ZV327cq9SW+5RNreY8Pnf2G09x63RXdK8DtusZ9a7nN8CLEfRm/D6CUS9IaEBI0AsyNiAkBJkel97uJDwgZYyo+H2c0O/RhyOfUEsDBBQAAAAIAIdO4kB/v9PKnQAAAOQAAAATAAAAW0NvbnRlbnRfVHlwZXNdLnhtbG2PSw7CMAxErxJ5n7qwQAg17aJwAy4QBfcjmo8aF4Xbk9AdYunxPM+46ZJdxIvWOHun4FDVIMgZ/5jdqGDjQZ6ha5v7O1AU2eqigok5XBCjmcjqWPlALm8Gv1rNeVxHDNo89Uh4rOsTGu+YHEsuN6BtrjTobWFxS1neYzMOot99JUoBU2IsMv4F7I9dh7DMRnN+ApO0UdoC4rd2+wFQSwECFAAUAAAACACHTuJAf7/Typ0AAADkAAAAEwAAAAAAAAABACAAAADyAgAAW0NvbnRlbnRfVHlwZXNdLnhtbFBLAQIUAAoAAAAAAIdO4kAAAAAAAAAAAAAAAAAHAAAAAAAAAAAAEAAAAAAAAABDb25maWcvUEsBAhQAFAAAAAgAh07iQBI4/pifAAAA8wAAABIAAAAAAAAAAQAgAAAAJQAAAENvbmZpZy9QYWNrYWdlLnhtbFBLAQIUAAoAAAAAAIdO4kAAAAAAAAAAAAAAAAAJAAAAAAAAAAAAEAAAAPQAAABGb3JtdWxhcy9QSwECFAAUAAAACACHTuJAvd0qtqYBAADvAwAAEwAAAAAAAAABACAAAAAbAQAARm9ybXVsYXMvU2VjdGlvbjEubVBLBQYAAAAABQAFAC4BAADAAwAAAAAOAQAAPD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXRmLTgiID8+PFBlcm1pc3Npb25MaXN0IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiPjxDYW5FdmFsdWF0ZUZ1dHVyZVBhY2thZ2VzPmZhbHNlPC9DYW5FdmFsdWF0ZUZ1dHVyZVBhY2thZ2VzPjxGaXJld2FsbEVuYWJsZWQ+dHJ1ZTwvRmlyZXdhbGxFbmFibGVkPjwvUGVybWlzc2lvbkxpc3Q+kwQAAAAAAABxBAAAPD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXRmLTgiID8+PExvY2FsUGFja2FnZU1ldGFkYXRhRmlsZSB4bWxuczp4c2Q9Imh0dHA6Ly93d3cudzMub3JnLzIwMDEvWE1MU2NoZW1hIiB4bWxuczp4c2k9Imh0dHA6Ly93d3cudzMub3JnLzIwMDEvWE1MU2NoZW1hLWluc3RhbmNlIj48SXRlbXM+PEl0ZW0+PEl0ZW1Mb2NhdGlvbj48SXRlbVR5cGU+QWxsRm9ybXVsYXM8L0l0ZW1UeXBlPjxJdGVtUGF0aCAvPjwvSXRlbUxvY2F0aW9uPjxTdGFibGVFbnRyaWVzPjxFbnRyeSBUeXBlPSJSZWxhdGlvbnNoaXBzIiBWYWx1ZT0ic0FBQUFBQT09IiAvPjwvU3RhYmxlRW50cmllcz48L0l0ZW0+PEl0ZW0+PEl0ZW1Mb2NhdGlvbj48SXRlbVR5cGU+Rm9ybXVsYTwvSXRlbVR5cGU+PEl0ZW1QYXRoPlNlY3Rpb24xLyVFMyU4MiVCQyVFMyU4MyU4RSVFMyU4MyU5NiVFMyU4MyVBQyVFMyU4MiVBNCVFMyU4MyU4OURFXyVFNCVCQiVCQiVFNSU4QSVBMSVFNyVBRSVBMSVFNyU5MCU4NiUyMCUyMHhsc3g8L0l0ZW1QYXRoPjwvSXRlbUxvY2F0aW9uPjxTdGFibGVFbnRyaWVzPjxFbnRyeSBUeXBlPSJJc1ByaXZhdGUiIFZhbHVlPSJsMCIgLz48RW50cnkgVHlwZT0iRmlsbEVuYWJsZWQiIFZhbHVlPSJsMSIgLz48RW50cnkgVHlwZT0iRmlsbE9iamVjdFR5cGUiIFZhbHVlPSJzVGFibGUiIC8+PEVudHJ5IFR5cGU9IlF1ZXJ5SUQiIFZhbHVlPSJzMzI0MDk1OTItMTBmMi00ZDk4LWI0OWQtNDlmNmQzYmIxMDAwIiAvPjxFbnRyeSBUeXBlPSJSZXN1bHRUeXBlIiBWYWx1ZT0ic1RhYmxlIiAvPjxFbnRyeSBUeXBlPSJGaWxsVGFyZ2V0IiBWYWx1ZT0ic+ihqF/jgrzjg47jg5bjg6zjgqTjg4lERV/ku7vliqHnrqHnkIZfX3hsc3giIC8+PEVudHJ5IFR5cGU9IkZpbGxDb3VudCIgVmFsdWU9ImwxNyIgLz48RW50cnkgVHlwZT0iRmlsbEVycm9yQ291bnQiIFZhbHVlPSJsMCIgLz48RW50cnkgVHlwZT0iRmlsbExhc3RVcGRhdGVkIiBWYWx1ZT0iZDIwMjYtMDUtMDZUMDU6MjE6MDMuNzY3MDAwMFoiIC8+PEVudHJ5IFR5cGU9IkZpbGxDb2x1bW5OYW1lcyIgVmFsdWU9J3NbJnF1b3Q75rGH5oC75LiA6KeIJnF1b3Q7XScgLz48L1N0YWJsZUVudHJpZXM+PC9JdGVtPjwvSXRlbXM+PC9Mb2NhbFBhY2thZ2VNZXRhZGF0YUZpbGU+FgAAAFBLBQYAAAAAAAAAAAAAAAAAAAAAAAAmAQAAAQAAANCMnd8BFdERjHoAwE/Cl+sBAAAA2cHvIhDB8U+DzvEXf4lk6wAAAAACAAAAAAAQZgAAAAEAACAAAAA8EpwDew2CDIUHW9ZgW/1ivK7bcOsRbu/0dTKCsyDKVQAAAAAOgAAAAAIAACAAAADw1c03kaCuNh2rscf2W7gcS8HVT5kX8OAabXguH3ZdzFAAAAD8+pPMzsPq2NyQPxxQPYekie7p1wlZI7QT2iitgNCb2E+8vmLv8/T4BdRuNuPEc024N7R9QPHeFZgwT6Va4N6jL9EN5EsINmOXTEmlOrrv20AAAADVyCmBuUhQ41WsUNSSUrPwREsPXRMXnFjZiBGb6tjMquyVC8luxc8zj0emh0OXNJevy+iEBzPq7r2uMgb27P+h</DataMashup>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A452D214-DA4F-4B05-9986-7FF769A56B3C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58AB6B07-D633-4F13-A540-283D7159BD8D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/DataMashup"/>
   </ds:schemaRefs>

--- a/记录人生/01游戏攻略/异度之刃/ゼノブレイドDE_任务管理..xlsx
+++ b/记录人生/01游戏攻略/异度之刃/ゼノブレイドDE_任务管理..xlsx
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1695" uniqueCount="695">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1716" uniqueCount="695">
   <si>
     <t>汇总一览</t>
   </si>
@@ -758,36 +758,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>真</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>伝説のエンプレス</t>
-    </r>
+    <t>真・伝説のエンプレス</t>
   </si>
   <si>
     <t>高嶺の花への花</t>
@@ -3799,6 +3770,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6">
       <alignment vertical="center"/>
     </xf>
@@ -3806,9 +3780,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
@@ -3835,13 +3806,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4145,12 +4116,9 @@
     <filterColumn colId="3">
       <filters>
         <filter val="0%"/>
-        <filter val="49%"/>
-        <filter val="79%"/>
-        <filter val="89%"/>
-        <filter val="90%"/>
-        <filter val="91%"/>
-        <filter val="92%"/>
+        <filter val="51%"/>
+        <filter val="97%"/>
+        <filter val="98%"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -4176,7 +4144,11 @@
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="表6_912" displayName="表6_912" ref="A5:C89" totalsRowShown="0">
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A5:C89" etc:filterBottomFollowUsedRange="0"/>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A5:C89" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="2">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="3">
     <tableColumn id="1" name="编号"/>
     <tableColumn id="2" name="任务名称"/>
@@ -4749,7 +4721,7 @@
       <c r="A3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="18" t="str">
+      <c r="B3" s="20" t="str">
         <f t="shared" si="0"/>
         <v>テフラ洞窟-任務</v>
       </c>
@@ -4770,17 +4742,17 @@
       <c r="A4" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="20" t="str">
+      <c r="B4" s="18" t="str">
         <f t="shared" si="0"/>
         <v>巨神脚-任務</v>
       </c>
       <c r="C4" s="14">
         <f ca="1" t="shared" si="1"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D4" s="19">
         <f ca="1" t="shared" si="2"/>
-        <v>0.947368421052632</v>
+        <v>0.973684210526316</v>
       </c>
       <c r="E4" s="14">
         <f ca="1" t="shared" si="3"/>
@@ -4791,17 +4763,17 @@
       <c r="A5" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="20" t="str">
+      <c r="B5" s="18" t="str">
         <f t="shared" si="0"/>
         <v>コロニー6-任務</v>
       </c>
       <c r="C5" s="14">
         <f ca="1" t="shared" si="1"/>
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D5" s="19">
         <f ca="1" t="shared" si="2"/>
-        <v>0.492537313432836</v>
+        <v>0.597014925373134</v>
       </c>
       <c r="E5" s="14">
         <f ca="1" t="shared" si="3"/>
@@ -4812,7 +4784,7 @@
       <c r="A6" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="20" t="str">
+      <c r="B6" s="18" t="str">
         <f t="shared" si="0"/>
         <v>燐光の地ザトール-任務</v>
       </c>
@@ -4829,7 +4801,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" hidden="1" spans="1:5">
       <c r="A7" s="14" t="s">
         <v>10</v>
       </c>
@@ -4839,18 +4811,18 @@
       </c>
       <c r="C7" s="14">
         <f ca="1" t="shared" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" s="19">
         <f ca="1" t="shared" si="2"/>
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E7" s="14">
         <f ca="1" t="shared" si="3"/>
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" hidden="1" spans="1:5">
       <c r="A8" s="14" t="s">
         <v>11</v>
       </c>
@@ -4860,32 +4832,32 @@
       </c>
       <c r="C8" s="14">
         <f ca="1" t="shared" si="1"/>
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="D8" s="19">
         <f ca="1" t="shared" si="2"/>
-        <v>0.916666666666667</v>
+        <v>1</v>
       </c>
       <c r="E8" s="14">
         <f ca="1" t="shared" si="3"/>
         <v>84</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" hidden="1" spans="1:5">
       <c r="A9" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="20" t="str">
+      <c r="B9" s="18" t="str">
         <f t="shared" si="0"/>
         <v>エルト海-任務</v>
       </c>
       <c r="C9" s="14">
         <f ca="1" t="shared" si="1"/>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D9" s="19">
         <f ca="1" t="shared" si="2"/>
-        <v>0.789473684210526</v>
+        <v>1</v>
       </c>
       <c r="E9" s="14">
         <f ca="1" t="shared" si="3"/>
@@ -4896,7 +4868,7 @@
       <c r="A10" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="18" t="str">
+      <c r="B10" s="20" t="str">
         <f t="shared" si="0"/>
         <v>皇都アカモート-任務</v>
       </c>
@@ -4917,7 +4889,7 @@
       <c r="A11" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="18" t="str">
+      <c r="B11" s="20" t="str">
         <f t="shared" si="0"/>
         <v>ヴァラク雪山-任務</v>
       </c>
@@ -4938,7 +4910,7 @@
       <c r="A12" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="18" t="str">
+      <c r="B12" s="20" t="str">
         <f t="shared" si="0"/>
         <v>大剣の渓谷-任務</v>
       </c>
@@ -4959,7 +4931,7 @@
       <c r="A13" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="18" t="str">
+      <c r="B13" s="20" t="str">
         <f t="shared" si="0"/>
         <v>ガラハド要塞-任務</v>
       </c>
@@ -4980,7 +4952,7 @@
       <c r="A14" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="20" t="str">
+      <c r="B14" s="18" t="str">
         <f t="shared" si="0"/>
         <v>落ちた腕-任務</v>
       </c>
@@ -5001,7 +4973,7 @@
       <c r="A15" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="18" t="str">
+      <c r="B15" s="20" t="str">
         <f t="shared" si="0"/>
         <v>機神界フィールド-任務</v>
       </c>
@@ -5022,7 +4994,7 @@
       <c r="A16" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="18" t="str">
+      <c r="B16" s="20" t="str">
         <f t="shared" si="0"/>
         <v>中央工廠-任務</v>
       </c>
@@ -5043,7 +5015,7 @@
       <c r="A17" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="20" t="str">
+      <c r="B17" s="18" t="str">
         <f t="shared" si="0"/>
         <v>帝都アグニラータ-任務</v>
       </c>
@@ -5064,7 +5036,7 @@
       <c r="A18" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="18" t="str">
+      <c r="B18" s="20" t="str">
         <f t="shared" si="0"/>
         <v>監獄島(2回目)-任務</v>
       </c>
@@ -5086,15 +5058,15 @@
       <c r="B19" s="21"/>
       <c r="C19" s="14">
         <f ca="1">SUBTOTAL(109,表_ゼノブレイドDE_任务管理__xlsx[已完成任务])</f>
-        <v>249</v>
+        <v>156</v>
       </c>
       <c r="D19" s="22">
         <f ca="1">表_ゼノブレイドDE_任务管理__xlsx[[#Totals],[已完成任务]]/表_ゼノブレイドDE_任务管理__xlsx[[#Totals],[总数]]</f>
-        <v>0.827242524916943</v>
+        <v>0.829787234042553</v>
       </c>
       <c r="E19">
         <f ca="1">SUBTOTAL(109,表_ゼノブレイドDE_任务管理__xlsx[总数])</f>
-        <v>301</v>
+        <v>188</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -5204,10 +5176,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="6"/>
+      <c r="B1" s="7"/>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
@@ -5254,7 +5226,7 @@
       <c r="B6" t="s">
         <v>370</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5265,7 +5237,7 @@
       <c r="B7" t="s">
         <v>371</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5276,7 +5248,7 @@
       <c r="B8" t="s">
         <v>372</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5287,7 +5259,7 @@
       <c r="B9" t="s">
         <v>373</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>46</v>
       </c>
       <c r="I9">
@@ -5301,7 +5273,7 @@
       <c r="B10" t="s">
         <v>374</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="8" t="s">
         <v>46</v>
       </c>
       <c r="J10">
@@ -5318,7 +5290,7 @@
       <c r="B11" t="s">
         <v>375</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="8" t="s">
         <v>46</v>
       </c>
       <c r="J11">
@@ -5335,7 +5307,7 @@
       <c r="B12" t="s">
         <v>376</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="8" t="s">
         <v>46</v>
       </c>
       <c r="J12">
@@ -5352,7 +5324,7 @@
       <c r="B13" t="s">
         <v>377</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="8" t="s">
         <v>46</v>
       </c>
       <c r="J13">
@@ -5369,7 +5341,7 @@
       <c r="B14" t="s">
         <v>378</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="8" t="s">
         <v>46</v>
       </c>
       <c r="J14">
@@ -5386,7 +5358,7 @@
       <c r="B15" t="s">
         <v>379</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5397,7 +5369,7 @@
       <c r="B16" t="s">
         <v>380</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5408,7 +5380,7 @@
       <c r="B17" t="s">
         <v>381</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5419,7 +5391,7 @@
       <c r="B18" t="s">
         <v>382</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5430,7 +5402,7 @@
       <c r="B19" t="s">
         <v>383</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5441,7 +5413,7 @@
       <c r="B20" t="s">
         <v>384</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5452,7 +5424,7 @@
       <c r="B21" t="s">
         <v>385</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5463,7 +5435,7 @@
       <c r="B22" t="s">
         <v>386</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5474,7 +5446,7 @@
       <c r="B23" t="s">
         <v>387</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5485,7 +5457,7 @@
       <c r="B24" t="s">
         <v>388</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5496,7 +5468,7 @@
       <c r="B25" t="s">
         <v>389</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5507,7 +5479,7 @@
       <c r="B26" t="s">
         <v>390</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5518,7 +5490,7 @@
       <c r="B27" t="s">
         <v>391</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5529,7 +5501,7 @@
       <c r="B28" t="s">
         <v>392</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5540,7 +5512,7 @@
       <c r="B29" t="s">
         <v>393</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5551,7 +5523,7 @@
       <c r="B30" t="s">
         <v>394</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5562,7 +5534,7 @@
       <c r="B31" t="s">
         <v>395</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5573,7 +5545,7 @@
       <c r="B32" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5584,7 +5556,7 @@
       <c r="B33" t="s">
         <v>397</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C33" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5595,7 +5567,7 @@
       <c r="B34" t="s">
         <v>96</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C34" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5606,7 +5578,7 @@
       <c r="B35" t="s">
         <v>97</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C35" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5617,7 +5589,7 @@
       <c r="B36" t="s">
         <v>98</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C36" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5628,7 +5600,7 @@
       <c r="B37" t="s">
         <v>99</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C37" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5639,7 +5611,7 @@
       <c r="B38" t="s">
         <v>100</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C38" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5650,7 +5622,7 @@
       <c r="B39" t="s">
         <v>101</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C39" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5661,7 +5633,7 @@
       <c r="B40" t="s">
         <v>102</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C40" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5672,7 +5644,7 @@
       <c r="B41" t="s">
         <v>103</v>
       </c>
-      <c r="C41" s="7" t="s">
+      <c r="C41" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5683,7 +5655,7 @@
       <c r="B42" t="s">
         <v>104</v>
       </c>
-      <c r="C42" s="7" t="s">
+      <c r="C42" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5694,7 +5666,7 @@
       <c r="B43" t="s">
         <v>106</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C43" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5705,7 +5677,7 @@
       <c r="B44" t="s">
         <v>107</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="C44" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5716,7 +5688,7 @@
       <c r="B45" t="s">
         <v>108</v>
       </c>
-      <c r="C45" s="7" t="s">
+      <c r="C45" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5727,7 +5699,7 @@
       <c r="B46" t="s">
         <v>109</v>
       </c>
-      <c r="C46" s="7" t="s">
+      <c r="C46" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5738,7 +5710,7 @@
       <c r="B47" t="s">
         <v>110</v>
       </c>
-      <c r="C47" s="7" t="s">
+      <c r="C47" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5749,7 +5721,7 @@
       <c r="B48" t="s">
         <v>111</v>
       </c>
-      <c r="C48" s="7" t="s">
+      <c r="C48" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5760,7 +5732,7 @@
       <c r="B49" t="s">
         <v>112</v>
       </c>
-      <c r="C49" s="7" t="s">
+      <c r="C49" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5771,7 +5743,7 @@
       <c r="B50" t="s">
         <v>113</v>
       </c>
-      <c r="C50" s="7" t="s">
+      <c r="C50" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5782,7 +5754,7 @@
       <c r="B51" t="s">
         <v>114</v>
       </c>
-      <c r="C51" s="7" t="s">
+      <c r="C51" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5793,7 +5765,7 @@
       <c r="B52" t="s">
         <v>115</v>
       </c>
-      <c r="C52" s="7" t="s">
+      <c r="C52" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5804,7 +5776,7 @@
       <c r="B53" t="s">
         <v>116</v>
       </c>
-      <c r="C53" s="7" t="s">
+      <c r="C53" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5815,7 +5787,7 @@
       <c r="B54" t="s">
         <v>117</v>
       </c>
-      <c r="C54" s="7" t="s">
+      <c r="C54" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5826,7 +5798,7 @@
       <c r="B55" t="s">
         <v>118</v>
       </c>
-      <c r="C55" s="7" t="s">
+      <c r="C55" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5837,7 +5809,7 @@
       <c r="B56" t="s">
         <v>119</v>
       </c>
-      <c r="C56" s="7" t="s">
+      <c r="C56" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5848,7 +5820,7 @@
       <c r="B57" t="s">
         <v>120</v>
       </c>
-      <c r="C57" s="7" t="s">
+      <c r="C57" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5859,7 +5831,7 @@
       <c r="B58" t="s">
         <v>121</v>
       </c>
-      <c r="C58" s="7" t="s">
+      <c r="C58" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5870,7 +5842,7 @@
       <c r="B59" t="s">
         <v>122</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="C59" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5881,7 +5853,7 @@
       <c r="B60" t="s">
         <v>123</v>
       </c>
-      <c r="C60" s="7" t="s">
+      <c r="C60" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5892,7 +5864,7 @@
       <c r="B61" t="s">
         <v>124</v>
       </c>
-      <c r="C61" s="7" t="s">
+      <c r="C61" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5929,10 +5901,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="6"/>
+      <c r="B1" s="7"/>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
@@ -5979,7 +5951,7 @@
       <c r="B6" t="s">
         <v>398</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5990,7 +5962,7 @@
       <c r="B7" t="s">
         <v>399</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6001,7 +5973,7 @@
       <c r="B8" t="s">
         <v>400</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6012,7 +5984,7 @@
       <c r="B9" t="s">
         <v>401</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6023,7 +5995,7 @@
       <c r="B10" t="s">
         <v>402</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6034,7 +6006,7 @@
       <c r="B11" t="s">
         <v>403</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6045,7 +6017,7 @@
       <c r="B12" t="s">
         <v>404</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6056,7 +6028,7 @@
       <c r="B13" t="s">
         <v>405</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6067,7 +6039,7 @@
       <c r="B14" t="s">
         <v>406</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6078,7 +6050,7 @@
       <c r="B15" t="s">
         <v>407</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6089,7 +6061,7 @@
       <c r="B16" t="s">
         <v>161</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6100,7 +6072,7 @@
       <c r="B17" t="s">
         <v>408</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6111,7 +6083,7 @@
       <c r="B18" t="s">
         <v>409</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6122,7 +6094,7 @@
       <c r="B19" t="s">
         <v>410</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6159,10 +6131,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="6"/>
+      <c r="B1" s="7"/>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
@@ -6209,7 +6181,7 @@
       <c r="B6" t="s">
         <v>411</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6220,7 +6192,7 @@
       <c r="B7" t="s">
         <v>412</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6231,7 +6203,7 @@
       <c r="B8" t="s">
         <v>413</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6242,7 +6214,7 @@
       <c r="B9" t="s">
         <v>414</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6279,10 +6251,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="6"/>
+      <c r="B1" s="7"/>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
@@ -6329,7 +6301,7 @@
       <c r="B6" t="s">
         <v>415</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6340,7 +6312,7 @@
       <c r="B7" t="s">
         <v>416</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6351,7 +6323,7 @@
       <c r="B8" t="s">
         <v>417</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6362,7 +6334,7 @@
       <c r="B9" t="s">
         <v>418</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6449,7 +6421,7 @@
       <c r="B6" t="s">
         <v>419</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6460,7 +6432,7 @@
       <c r="B7" t="s">
         <v>420</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6471,7 +6443,7 @@
       <c r="B8" t="s">
         <v>421</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6482,7 +6454,7 @@
       <c r="B9" t="s">
         <v>422</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6493,7 +6465,7 @@
       <c r="B10" t="s">
         <v>423</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6504,7 +6476,7 @@
       <c r="B11" s="5" t="s">
         <v>424</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6515,7 +6487,7 @@
       <c r="B12" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6526,7 +6498,7 @@
       <c r="B13" s="5" t="s">
         <v>426</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6537,7 +6509,7 @@
       <c r="B14" s="5" t="s">
         <v>427</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6548,7 +6520,7 @@
       <c r="B15" t="s">
         <v>428</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6559,7 +6531,7 @@
       <c r="B16" t="s">
         <v>429</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6570,7 +6542,7 @@
       <c r="B17" t="s">
         <v>430</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6581,7 +6553,7 @@
       <c r="B18" t="s">
         <v>431</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6592,7 +6564,7 @@
       <c r="B19" t="s">
         <v>432</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6603,7 +6575,7 @@
       <c r="B20" t="s">
         <v>433</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6614,7 +6586,7 @@
       <c r="B21" t="s">
         <v>434</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6625,7 +6597,7 @@
       <c r="B22" t="s">
         <v>435</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6636,7 +6608,7 @@
       <c r="B23" t="s">
         <v>436</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6647,7 +6619,7 @@
       <c r="B24" t="s">
         <v>437</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6658,7 +6630,7 @@
       <c r="B25" t="s">
         <v>438</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6669,7 +6641,7 @@
       <c r="B26" t="s">
         <v>439</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6680,7 +6652,7 @@
       <c r="B27" t="s">
         <v>440</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6691,7 +6663,7 @@
       <c r="B28" t="s">
         <v>441</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6702,7 +6674,7 @@
       <c r="B29" t="s">
         <v>442</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6713,7 +6685,7 @@
       <c r="B30" t="s">
         <v>443</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6724,7 +6696,7 @@
       <c r="B31" t="s">
         <v>444</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6735,7 +6707,7 @@
       <c r="B32" t="s">
         <v>445</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6746,7 +6718,7 @@
       <c r="B33" t="s">
         <v>446</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C33" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6757,7 +6729,7 @@
       <c r="B34" t="s">
         <v>447</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C34" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6768,7 +6740,7 @@
       <c r="B35" t="s">
         <v>448</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C35" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6805,10 +6777,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="6"/>
+      <c r="B1" s="7"/>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
@@ -6855,7 +6827,7 @@
       <c r="B6" t="s">
         <v>449</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6866,7 +6838,7 @@
       <c r="B7" t="s">
         <v>450</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6877,7 +6849,7 @@
       <c r="B8" t="s">
         <v>451</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6888,7 +6860,7 @@
       <c r="B9" t="s">
         <v>452</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6899,7 +6871,7 @@
       <c r="B10" t="s">
         <v>453</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6910,7 +6882,7 @@
       <c r="B11" t="s">
         <v>454</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6921,7 +6893,7 @@
       <c r="B12" t="s">
         <v>455</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6932,7 +6904,7 @@
       <c r="B13" t="s">
         <v>456</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -6943,7 +6915,7 @@
       <c r="B14" t="s">
         <v>457</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -7030,7 +7002,7 @@
       <c r="B6" t="s">
         <v>458</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -7041,7 +7013,7 @@
       <c r="B7" t="s">
         <v>459</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -7052,7 +7024,7 @@
       <c r="B8" t="s">
         <v>460</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -7063,7 +7035,7 @@
       <c r="B9" t="s">
         <v>461</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -7074,7 +7046,7 @@
       <c r="B10" t="s">
         <v>462</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -7085,7 +7057,7 @@
       <c r="B11" t="s">
         <v>463</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -7096,7 +7068,7 @@
       <c r="B12" t="s">
         <v>464</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -7107,7 +7079,7 @@
       <c r="B13" t="s">
         <v>465</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -7118,7 +7090,7 @@
       <c r="B14" t="s">
         <v>466</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -7205,7 +7177,7 @@
       <c r="B6" t="s">
         <v>467</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -7216,7 +7188,7 @@
       <c r="B7" t="s">
         <v>468</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -7227,7 +7199,7 @@
       <c r="B8" t="s">
         <v>469</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -7238,7 +7210,7 @@
       <c r="B9" t="s">
         <v>470</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -7249,7 +7221,7 @@
       <c r="B10" t="s">
         <v>471</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -7260,7 +7232,7 @@
       <c r="B11" t="s">
         <v>472</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -7271,7 +7243,7 @@
       <c r="B12" t="s">
         <v>473</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -7282,7 +7254,7 @@
       <c r="B13" t="s">
         <v>474</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -7293,7 +7265,7 @@
       <c r="B14" t="s">
         <v>475</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -7304,7 +7276,7 @@
       <c r="B15" t="s">
         <v>476</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -7315,7 +7287,7 @@
       <c r="B16" t="s">
         <v>477</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -7326,7 +7298,7 @@
       <c r="B17" t="s">
         <v>478</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -7337,7 +7309,7 @@
       <c r="B18" t="s">
         <v>479</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -7348,7 +7320,7 @@
       <c r="B19" t="s">
         <v>480</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -7359,7 +7331,7 @@
       <c r="B20" t="s">
         <v>481</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -7370,7 +7342,7 @@
       <c r="B21" t="s">
         <v>482</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -7381,7 +7353,7 @@
       <c r="B22" t="s">
         <v>483</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -7418,10 +7390,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="6"/>
+      <c r="B1" s="7"/>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
@@ -7468,7 +7440,7 @@
       <c r="B6" s="4" t="s">
         <v>484</v>
       </c>
-      <c r="C6" s="7"/>
+      <c r="C6" s="8"/>
     </row>
     <row r="7" ht="16.5" customHeight="1" spans="1:3">
       <c r="A7">
@@ -7477,7 +7449,7 @@
       <c r="B7" s="4" t="s">
         <v>485</v>
       </c>
-      <c r="C7" s="7"/>
+      <c r="C7" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7512,7 +7484,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B1" s="6"/>
@@ -8895,7 +8867,7 @@
       </c>
       <c r="B2">
         <f>COUNTIF(表16[完成情况],"〇")</f>
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -8904,7 +8876,7 @@
       </c>
       <c r="B3">
         <f>COUNTIF(表16[完成情况],"✕")+COUNTIF(表16[完成情况],"")</f>
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -8913,7 +8885,7 @@
       </c>
       <c r="B4" s="3">
         <f>B2/MAX(表16[编号])</f>
-        <v>0.732484076433121</v>
+        <v>0.751592356687898</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -9945,6 +9917,9 @@
       <c r="C81" t="s">
         <v>609</v>
       </c>
+      <c r="D81" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82">
@@ -9970,6 +9945,9 @@
       <c r="C83" t="s">
         <v>611</v>
       </c>
+      <c r="D83" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84">
@@ -10175,6 +10153,9 @@
       </c>
       <c r="C99" t="s">
         <v>629</v>
+      </c>
+      <c r="D99" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -11007,7 +10988,7 @@
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D6:D22 D23:D24 D25:D28 D29:D30 D31:D72 D73:D74 D75:D131 D132:D133 D134:D162">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D6:D22 D23:D24 D25:D28 D29:D30 D31:D72 D73:D74 D75:D79 D80:D81 D82:D131 D132:D133 D134:D162">
       <formula1>"〇,✕"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11086,7 +11067,7 @@
       <c r="B6" t="s">
         <v>128</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -11097,7 +11078,7 @@
       <c r="B7" t="s">
         <v>129</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -11108,7 +11089,7 @@
       <c r="B8" t="s">
         <v>130</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -11119,7 +11100,7 @@
       <c r="B9" t="s">
         <v>131</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -11130,7 +11111,7 @@
       <c r="B10" t="s">
         <v>132</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -11141,7 +11122,7 @@
       <c r="B11" t="s">
         <v>133</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -11152,7 +11133,7 @@
       <c r="B12" t="s">
         <v>134</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -11163,7 +11144,7 @@
       <c r="B13" t="s">
         <v>135</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -11174,7 +11155,7 @@
       <c r="B14" t="s">
         <v>136</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -11185,7 +11166,7 @@
       <c r="B15" t="s">
         <v>137</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -11196,7 +11177,7 @@
       <c r="B16" t="s">
         <v>138</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -11207,7 +11188,7 @@
       <c r="B17" t="s">
         <v>139</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -11218,7 +11199,7 @@
       <c r="B18" t="s">
         <v>140</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -11258,7 +11239,7 @@
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="9"/>
+      <c r="B1" s="6"/>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
@@ -11266,7 +11247,7 @@
       </c>
       <c r="B2">
         <f>COUNTIF(表4[完成情况],"〇")</f>
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -11275,7 +11256,7 @@
       </c>
       <c r="B3">
         <f>COUNTIF(表4[完成情况],"✕")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -11284,7 +11265,7 @@
       </c>
       <c r="B4" s="3">
         <f>B2/MAX(表4[编号])</f>
-        <v>0.947368421052632</v>
+        <v>0.973684210526316</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -11349,7 +11330,7 @@
       <c r="B10" t="s">
         <v>145</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -11470,7 +11451,7 @@
       <c r="B21" t="s">
         <v>156</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="8" t="s">
         <v>65</v>
       </c>
     </row>
@@ -11481,7 +11462,7 @@
       <c r="B22" t="s">
         <v>157</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -11492,7 +11473,7 @@
       <c r="B23" t="s">
         <v>158</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -11503,8 +11484,8 @@
       <c r="B24" t="s">
         <v>159</v>
       </c>
-      <c r="C24" s="7" t="s">
-        <v>65</v>
+      <c r="C24" s="8" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="25" hidden="1" spans="1:3">
@@ -11721,7 +11702,7 @@
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6:C21 C22:C23 C24:C43">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C22 C6:C21 C23:C24 C25:C43">
       <formula1>"〇,✕"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11754,7 +11735,7 @@
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="9"/>
+      <c r="B1" s="6"/>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
@@ -11762,7 +11743,7 @@
       </c>
       <c r="B2">
         <f>COUNTIF(表5[完成情况],"〇")</f>
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -11771,7 +11752,7 @@
       </c>
       <c r="B3">
         <f>COUNTIF(表5[完成情况],"✕")</f>
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -11780,7 +11761,7 @@
       </c>
       <c r="B4" s="3">
         <f>B2/MAX(表5[编号])</f>
-        <v>0.492537313432836</v>
+        <v>0.597014925373134</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:9">
@@ -11813,7 +11794,7 @@
       <c r="B6" t="s">
         <v>168</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>46</v>
       </c>
       <c r="F6" t="s">
@@ -11821,6 +11802,9 @@
       </c>
       <c r="G6" t="s">
         <v>170</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:9">
@@ -11830,7 +11814,7 @@
       <c r="B7" t="s">
         <v>171</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>46</v>
       </c>
       <c r="F7" t="s">
@@ -11839,7 +11823,7 @@
       <c r="G7" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -11850,7 +11834,7 @@
       <c r="B8" t="s">
         <v>173</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>46</v>
       </c>
       <c r="F8" t="s">
@@ -11858,6 +11842,9 @@
       </c>
       <c r="G8" s="5" t="s">
         <v>174</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:9">
@@ -11867,7 +11854,7 @@
       <c r="B9" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>46</v>
       </c>
       <c r="F9" t="s">
@@ -11875,6 +11862,9 @@
       </c>
       <c r="G9" t="s">
         <v>176</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:9">
@@ -11884,7 +11874,7 @@
       <c r="B10" t="s">
         <v>177</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="8" t="s">
         <v>46</v>
       </c>
       <c r="F10" t="s">
@@ -11901,7 +11891,7 @@
       <c r="B11" t="s">
         <v>179</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="8" t="s">
         <v>46</v>
       </c>
       <c r="F11" t="s">
@@ -11909,6 +11899,9 @@
       </c>
       <c r="G11" t="s">
         <v>180</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:9">
@@ -11918,7 +11911,7 @@
       <c r="B12" t="s">
         <v>181</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="8" t="s">
         <v>46</v>
       </c>
       <c r="F12" t="s">
@@ -11926,6 +11919,9 @@
       </c>
       <c r="G12" t="s">
         <v>182</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:9">
@@ -11935,7 +11931,7 @@
       <c r="B13" t="s">
         <v>183</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="8" t="s">
         <v>46</v>
       </c>
       <c r="F13" t="s">
@@ -11944,7 +11940,7 @@
       <c r="G13" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="H13" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -11955,7 +11951,7 @@
       <c r="B14" t="s">
         <v>186</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="8" t="s">
         <v>46</v>
       </c>
       <c r="F14" t="s">
@@ -11964,7 +11960,7 @@
       <c r="G14" t="s">
         <v>187</v>
       </c>
-      <c r="H14" s="7" t="s">
+      <c r="H14" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -11975,7 +11971,7 @@
       <c r="B15" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="8" t="s">
         <v>46</v>
       </c>
       <c r="F15" t="s">
@@ -11984,7 +11980,7 @@
       <c r="G15" t="s">
         <v>189</v>
       </c>
-      <c r="H15" s="7" t="s">
+      <c r="H15" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -11995,7 +11991,7 @@
       <c r="B16" t="s">
         <v>190</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="8" t="s">
         <v>46</v>
       </c>
       <c r="F16" t="s">
@@ -12004,7 +12000,7 @@
       <c r="G16" t="s">
         <v>191</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="H16" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -12015,7 +12011,7 @@
       <c r="B17" t="s">
         <v>192</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="8" t="s">
         <v>46</v>
       </c>
       <c r="F17" t="s">
@@ -12032,7 +12028,7 @@
       <c r="B18" t="s">
         <v>194</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="8" t="s">
         <v>46</v>
       </c>
       <c r="F18" t="s">
@@ -12049,7 +12045,7 @@
       <c r="B19" t="s">
         <v>196</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="8" t="s">
         <v>46</v>
       </c>
       <c r="F19" t="s">
@@ -12058,7 +12054,7 @@
       <c r="G19" t="s">
         <v>198</v>
       </c>
-      <c r="H19" s="7" t="s">
+      <c r="H19" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -12069,7 +12065,7 @@
       <c r="B20" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="8" t="s">
         <v>46</v>
       </c>
       <c r="F20" t="s">
@@ -12078,7 +12074,7 @@
       <c r="G20" t="s">
         <v>200</v>
       </c>
-      <c r="H20" s="7" t="s">
+      <c r="H20" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -12089,7 +12085,7 @@
       <c r="B21" t="s">
         <v>201</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="8" t="s">
         <v>46</v>
       </c>
       <c r="F21" t="s">
@@ -12097,6 +12093,9 @@
       </c>
       <c r="G21" t="s">
         <v>202</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:9">
@@ -12106,7 +12105,7 @@
       <c r="B22" t="s">
         <v>203</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="8" t="s">
         <v>46</v>
       </c>
       <c r="F22" t="s">
@@ -12126,7 +12125,7 @@
       <c r="B23" t="s">
         <v>206</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="8" t="s">
         <v>46</v>
       </c>
       <c r="F23" t="s">
@@ -12143,8 +12142,8 @@
       <c r="B24" t="s">
         <v>208</v>
       </c>
-      <c r="C24" s="7" t="s">
-        <v>65</v>
+      <c r="C24" s="8" t="s">
+        <v>46</v>
       </c>
       <c r="F24" t="s">
         <v>197</v>
@@ -12160,8 +12159,8 @@
       <c r="B25" t="s">
         <v>210</v>
       </c>
-      <c r="C25" s="7" t="s">
-        <v>65</v>
+      <c r="C25" s="8" t="s">
+        <v>46</v>
       </c>
       <c r="F25" t="s">
         <v>197</v>
@@ -12177,8 +12176,8 @@
       <c r="B26" t="s">
         <v>212</v>
       </c>
-      <c r="C26" s="7" t="s">
-        <v>65</v>
+      <c r="C26" s="8" t="s">
+        <v>46</v>
       </c>
       <c r="F26" t="s">
         <v>197</v>
@@ -12194,8 +12193,8 @@
       <c r="B27" t="s">
         <v>214</v>
       </c>
-      <c r="C27" s="7" t="s">
-        <v>65</v>
+      <c r="C27" s="8" t="s">
+        <v>46</v>
       </c>
       <c r="F27" t="s">
         <v>215</v>
@@ -12211,8 +12210,8 @@
       <c r="B28" t="s">
         <v>217</v>
       </c>
-      <c r="C28" s="7" t="s">
-        <v>65</v>
+      <c r="C28" s="8" t="s">
+        <v>46</v>
       </c>
       <c r="F28" t="s">
         <v>215</v>
@@ -12231,7 +12230,7 @@
       <c r="B29" t="s">
         <v>219</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="8" t="s">
         <v>65</v>
       </c>
     </row>
@@ -12242,7 +12241,7 @@
       <c r="B30" t="s">
         <v>220</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" s="8" t="s">
         <v>65</v>
       </c>
     </row>
@@ -12253,7 +12252,7 @@
       <c r="B31" t="s">
         <v>221</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" s="8" t="s">
         <v>65</v>
       </c>
     </row>
@@ -12264,7 +12263,7 @@
       <c r="B32" t="s">
         <v>222</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" s="8" t="s">
         <v>65</v>
       </c>
     </row>
@@ -12275,7 +12274,7 @@
       <c r="B33" t="s">
         <v>223</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C33" s="8" t="s">
         <v>65</v>
       </c>
     </row>
@@ -12286,7 +12285,7 @@
       <c r="B34" t="s">
         <v>224</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C34" s="8" t="s">
         <v>65</v>
       </c>
     </row>
@@ -12297,7 +12296,7 @@
       <c r="B35" t="s">
         <v>225</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C35" s="8" t="s">
         <v>65</v>
       </c>
     </row>
@@ -12308,7 +12307,7 @@
       <c r="B36" t="s">
         <v>226</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C36" s="8" t="s">
         <v>65</v>
       </c>
     </row>
@@ -12319,7 +12318,7 @@
       <c r="B37" t="s">
         <v>227</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C37" s="8" t="s">
         <v>65</v>
       </c>
     </row>
@@ -12330,7 +12329,7 @@
       <c r="B38" t="s">
         <v>228</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C38" s="8" t="s">
         <v>65</v>
       </c>
     </row>
@@ -12341,7 +12340,7 @@
       <c r="B39" t="s">
         <v>229</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C39" s="8" t="s">
         <v>65</v>
       </c>
     </row>
@@ -12352,7 +12351,7 @@
       <c r="B40" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C40" s="8" t="s">
         <v>65</v>
       </c>
     </row>
@@ -12363,7 +12362,7 @@
       <c r="B41" t="s">
         <v>231</v>
       </c>
-      <c r="C41" s="7" t="s">
+      <c r="C41" s="8" t="s">
         <v>65</v>
       </c>
     </row>
@@ -12374,7 +12373,7 @@
       <c r="B42" t="s">
         <v>232</v>
       </c>
-      <c r="C42" s="7" t="s">
+      <c r="C42" s="8" t="s">
         <v>65</v>
       </c>
     </row>
@@ -12385,7 +12384,7 @@
       <c r="B43" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C43" s="8" t="s">
         <v>65</v>
       </c>
     </row>
@@ -12396,7 +12395,7 @@
       <c r="B44" t="s">
         <v>234</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="C44" s="8" t="s">
         <v>65</v>
       </c>
     </row>
@@ -12407,7 +12406,7 @@
       <c r="B45" t="s">
         <v>235</v>
       </c>
-      <c r="C45" s="7" t="s">
+      <c r="C45" s="8" t="s">
         <v>65</v>
       </c>
     </row>
@@ -12418,7 +12417,7 @@
       <c r="B46" t="s">
         <v>236</v>
       </c>
-      <c r="C46" s="7" t="s">
+      <c r="C46" s="8" t="s">
         <v>65</v>
       </c>
     </row>
@@ -12429,7 +12428,7 @@
       <c r="B47" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="7" t="s">
+      <c r="C47" s="8" t="s">
         <v>65</v>
       </c>
     </row>
@@ -12440,7 +12439,7 @@
       <c r="B48" t="s">
         <v>238</v>
       </c>
-      <c r="C48" s="7" t="s">
+      <c r="C48" s="8" t="s">
         <v>65</v>
       </c>
     </row>
@@ -12451,7 +12450,7 @@
       <c r="B49" t="s">
         <v>239</v>
       </c>
-      <c r="C49" s="7" t="s">
+      <c r="C49" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -12462,7 +12461,7 @@
       <c r="B50" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="7" t="s">
+      <c r="C50" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -12473,7 +12472,7 @@
       <c r="B51" t="s">
         <v>241</v>
       </c>
-      <c r="C51" s="7" t="s">
+      <c r="C51" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -12484,7 +12483,7 @@
       <c r="B52" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="7" t="s">
+      <c r="C52" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -12495,7 +12494,7 @@
       <c r="B53" t="s">
         <v>243</v>
       </c>
-      <c r="C53" s="7" t="s">
+      <c r="C53" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -12506,7 +12505,7 @@
       <c r="B54" t="s">
         <v>244</v>
       </c>
-      <c r="C54" s="7" t="s">
+      <c r="C54" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -12517,7 +12516,7 @@
       <c r="B55" t="s">
         <v>245</v>
       </c>
-      <c r="C55" s="7" t="s">
+      <c r="C55" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -12528,7 +12527,7 @@
       <c r="B56" t="s">
         <v>246</v>
       </c>
-      <c r="C56" s="7" t="s">
+      <c r="C56" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -12539,7 +12538,7 @@
       <c r="B57" t="s">
         <v>247</v>
       </c>
-      <c r="C57" s="7" t="s">
+      <c r="C57" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -12550,7 +12549,7 @@
       <c r="B58" t="s">
         <v>248</v>
       </c>
-      <c r="C58" s="7" t="s">
+      <c r="C58" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -12561,7 +12560,7 @@
       <c r="B59" t="s">
         <v>249</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="C59" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -12572,7 +12571,7 @@
       <c r="B60" t="s">
         <v>250</v>
       </c>
-      <c r="C60" s="7" t="s">
+      <c r="C60" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -12583,7 +12582,7 @@
       <c r="B61" t="s">
         <v>251</v>
       </c>
-      <c r="C61" s="7" t="s">
+      <c r="C61" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -12594,7 +12593,7 @@
       <c r="B62" t="s">
         <v>252</v>
       </c>
-      <c r="C62" s="7" t="s">
+      <c r="C62" s="8" t="s">
         <v>65</v>
       </c>
     </row>
@@ -12605,7 +12604,7 @@
       <c r="B63" t="s">
         <v>253</v>
       </c>
-      <c r="C63" s="7" t="s">
+      <c r="C63" s="8" t="s">
         <v>65</v>
       </c>
     </row>
@@ -12616,7 +12615,7 @@
       <c r="B64" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="7" t="s">
+      <c r="C64" s="8" t="s">
         <v>65</v>
       </c>
     </row>
@@ -12627,7 +12626,7 @@
       <c r="B65" t="s">
         <v>255</v>
       </c>
-      <c r="C65" s="7" t="s">
+      <c r="C65" s="8" t="s">
         <v>65</v>
       </c>
     </row>
@@ -12638,7 +12637,7 @@
       <c r="B66" t="s">
         <v>256</v>
       </c>
-      <c r="C66" s="7" t="s">
+      <c r="C66" s="8" t="s">
         <v>65</v>
       </c>
     </row>
@@ -12649,8 +12648,8 @@
       <c r="B67" t="s">
         <v>257</v>
       </c>
-      <c r="C67" s="7" t="s">
-        <v>65</v>
+      <c r="C67" s="8" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="68" ht="16.5" spans="1:3">
@@ -12660,7 +12659,7 @@
       <c r="B68" t="s">
         <v>258</v>
       </c>
-      <c r="C68" s="7" t="s">
+      <c r="C68" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -12671,7 +12670,7 @@
       <c r="B69" t="s">
         <v>259</v>
       </c>
-      <c r="C69" s="7" t="s">
+      <c r="C69" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -12682,8 +12681,8 @@
       <c r="B70" t="s">
         <v>260</v>
       </c>
-      <c r="C70" s="7" t="s">
-        <v>65</v>
+      <c r="C70" s="8" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="71" ht="16.5" spans="1:3">
@@ -12693,7 +12692,7 @@
       <c r="B71" t="s">
         <v>261</v>
       </c>
-      <c r="C71" s="7" t="s">
+      <c r="C71" s="8" t="s">
         <v>65</v>
       </c>
     </row>
@@ -12704,7 +12703,7 @@
       <c r="B72" t="s">
         <v>262</v>
       </c>
-      <c r="C72" s="7" t="s">
+      <c r="C72" s="8" t="s">
         <v>65</v>
       </c>
     </row>
@@ -12713,7 +12712,7 @@
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H7 C19 C6:C18 C20:C21 C22:C23 C24:C72 H13:H16 H19:H20">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H6 H9 H11 H12 C19 H19 C22 C25 C26 C6:C18 C20:C21 C23:C24 C27:C28 C29:C68 C69:C70 C71:C72 H7:H8 H13:H16 H20:H21">
       <formula1>"〇,✕"</formula1>
     </dataValidation>
   </dataValidations>
@@ -12745,7 +12744,7 @@
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="9"/>
+      <c r="B1" s="6"/>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
@@ -12792,7 +12791,7 @@
       <c r="B6" t="s">
         <v>264</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -12803,7 +12802,7 @@
       <c r="B7" t="s">
         <v>265</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -12814,7 +12813,7 @@
       <c r="B8" t="s">
         <v>266</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -12825,7 +12824,7 @@
       <c r="B9" t="s">
         <v>267</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -12836,7 +12835,7 @@
       <c r="B10" t="s">
         <v>268</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -12847,7 +12846,7 @@
       <c r="B11" t="s">
         <v>269</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -12858,7 +12857,7 @@
       <c r="B12" t="s">
         <v>270</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -12869,7 +12868,7 @@
       <c r="B13" t="s">
         <v>271</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -12880,7 +12879,7 @@
       <c r="B14" t="s">
         <v>272</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -12891,7 +12890,7 @@
       <c r="B15" t="s">
         <v>273</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -12902,7 +12901,7 @@
       <c r="B16" t="s">
         <v>274</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -12913,7 +12912,7 @@
       <c r="B17" t="s">
         <v>275</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -12924,7 +12923,7 @@
       <c r="B18" t="s">
         <v>276</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -12935,7 +12934,7 @@
       <c r="B19" t="s">
         <v>277</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -12946,7 +12945,7 @@
       <c r="B20" t="s">
         <v>278</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -12957,7 +12956,7 @@
       <c r="B21" t="s">
         <v>279</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -12968,7 +12967,7 @@
       <c r="B22" t="s">
         <v>280</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -12979,7 +12978,7 @@
       <c r="B23" t="s">
         <v>281</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -12990,7 +12989,7 @@
       <c r="B24" t="s">
         <v>282</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -13001,7 +13000,7 @@
       <c r="B25" t="s">
         <v>283</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -13012,7 +13011,7 @@
       <c r="B26" t="s">
         <v>284</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -13023,7 +13022,7 @@
       <c r="B27" t="s">
         <v>285</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -13034,7 +13033,7 @@
       <c r="B28" t="s">
         <v>286</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -13071,7 +13070,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B1" s="6"/>
@@ -13082,7 +13081,7 @@
       </c>
       <c r="B2">
         <f>COUNTIF(表6_910[完成情况],"〇")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -13091,7 +13090,7 @@
       </c>
       <c r="B3">
         <f>COUNTIF(表6_910[完成情况],"✕")+COUNTIF(表6_910[完成情况],"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -13100,7 +13099,7 @@
       </c>
       <c r="B4" s="3">
         <f>B2/MAX(表6_910[编号])</f>
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -13121,7 +13120,7 @@
       <c r="B6" t="s">
         <v>287</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -13132,7 +13131,7 @@
       <c r="B7" t="s">
         <v>288</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -13143,7 +13142,9 @@
       <c r="B8" t="s">
         <v>289</v>
       </c>
-      <c r="C8" s="7"/>
+      <c r="C8" s="8" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="9" ht="16.5" spans="1:3">
       <c r="A9">
@@ -13152,7 +13153,7 @@
       <c r="B9" t="s">
         <v>290</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -13163,7 +13164,7 @@
       <c r="B10" t="s">
         <v>275</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -13174,7 +13175,7 @@
       <c r="B11" t="s">
         <v>276</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -13185,7 +13186,7 @@
       <c r="B12" t="s">
         <v>277</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -13196,7 +13197,7 @@
       <c r="B13" t="s">
         <v>278</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -13207,7 +13208,7 @@
       <c r="B14" t="s">
         <v>279</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -13218,12 +13219,12 @@
       <c r="B15" t="s">
         <v>291</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="8" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="42" ht="16.5" spans="1:1">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="9" t="s">
         <v>46</v>
       </c>
     </row>
@@ -13260,7 +13261,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B1" s="6"/>
@@ -13271,7 +13272,7 @@
       </c>
       <c r="B2">
         <f>COUNTIF(表6_912[完成情况],"〇")</f>
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -13280,7 +13281,7 @@
       </c>
       <c r="B3">
         <f>COUNTIF(表6_912[完成情况],"✕")+COUNTIF(表6_912[完成情况],"")</f>
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -13289,7 +13290,7 @@
       </c>
       <c r="B4" s="3">
         <f>B2/MAX(表6_912[编号])</f>
-        <v>0.916666666666667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -13303,356 +13304,356 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" ht="16.5" spans="1:5">
+    <row r="6" ht="16.5" hidden="1" spans="1:5">
       <c r="A6">
         <v>1</v>
       </c>
       <c r="B6" t="s">
         <v>292</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" spans="1:5">
+      <c r="C6" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5" hidden="1" spans="1:5">
       <c r="A7">
         <v>2</v>
       </c>
       <c r="B7" t="s">
         <v>293</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" ht="16.5" spans="1:5">
+      <c r="C7" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" hidden="1" spans="1:5">
       <c r="A8">
         <v>3</v>
       </c>
       <c r="B8" t="s">
         <v>294</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" ht="16.5" spans="1:5">
+      <c r="C8" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" hidden="1" spans="1:5">
       <c r="A9">
         <v>4</v>
       </c>
       <c r="B9" t="s">
         <v>295</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" ht="16.5" spans="1:5">
+      <c r="C9" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" hidden="1" spans="1:5">
       <c r="A10">
         <v>5</v>
       </c>
       <c r="B10" t="s">
         <v>296</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" ht="16.5" spans="1:5">
+      <c r="C10" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" hidden="1" spans="1:5">
       <c r="A11">
         <v>6</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="8" t="s">
         <v>46</v>
       </c>
       <c r="E11" s="4"/>
     </row>
-    <row r="12" ht="16.5" spans="1:5">
+    <row r="12" ht="16.5" hidden="1" spans="1:5">
       <c r="A12">
         <v>7</v>
       </c>
       <c r="B12" t="s">
         <v>298</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" ht="16.5" spans="1:5">
+      <c r="C12" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" hidden="1" spans="1:5">
       <c r="A13">
         <v>8</v>
       </c>
       <c r="B13" t="s">
         <v>299</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" ht="16.5" spans="1:5">
+      <c r="C13" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" hidden="1" spans="1:5">
       <c r="A14">
         <v>9</v>
       </c>
       <c r="B14" t="s">
         <v>300</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="15" ht="16.5" spans="1:5">
+      <c r="C14" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" hidden="1" spans="1:5">
       <c r="A15">
         <v>10</v>
       </c>
       <c r="B15" t="s">
         <v>301</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" ht="16.5" spans="1:5">
+      <c r="C15" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" ht="16.5" hidden="1" spans="1:5">
       <c r="A16">
         <v>11</v>
       </c>
       <c r="B16" t="s">
         <v>302</v>
       </c>
-      <c r="C16" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" ht="16.5" spans="1:3">
+      <c r="C16" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" ht="16.5" hidden="1" spans="1:3">
       <c r="A17">
         <v>12</v>
       </c>
       <c r="B17" t="s">
         <v>303</v>
       </c>
-      <c r="C17" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="18" ht="16.5" spans="1:3">
+      <c r="C17" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" ht="16.5" hidden="1" spans="1:3">
       <c r="A18">
         <v>13</v>
       </c>
       <c r="B18" t="s">
         <v>304</v>
       </c>
-      <c r="C18" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="19" ht="16.5" spans="1:3">
+      <c r="C18" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" ht="16.5" hidden="1" spans="1:3">
       <c r="A19">
         <v>14</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="C19" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="20" ht="16.5" spans="1:3">
+      <c r="C19" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" ht="16.5" hidden="1" spans="1:3">
       <c r="A20">
         <v>15</v>
       </c>
       <c r="B20" t="s">
         <v>306</v>
       </c>
-      <c r="C20" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="21" ht="16.5" spans="1:3">
+      <c r="C20" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" ht="16.5" hidden="1" spans="1:3">
       <c r="A21">
         <v>16</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="C21" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="22" ht="16.5" spans="1:3">
+      <c r="C21" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" ht="16.5" hidden="1" spans="1:3">
       <c r="A22">
         <v>17</v>
       </c>
       <c r="B22" t="s">
         <v>308</v>
       </c>
-      <c r="C22" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="23" ht="16.5" spans="1:3">
+      <c r="C22" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" ht="16.5" hidden="1" spans="1:3">
       <c r="A23">
         <v>18</v>
       </c>
       <c r="B23" t="s">
         <v>309</v>
       </c>
-      <c r="C23" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="24" ht="16.5" spans="1:3">
+      <c r="C23" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" ht="16.5" hidden="1" spans="1:3">
       <c r="A24">
         <v>19</v>
       </c>
       <c r="B24" t="s">
         <v>310</v>
       </c>
-      <c r="C24" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="25" ht="16.5" spans="1:3">
+      <c r="C24" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" ht="16.5" hidden="1" spans="1:3">
       <c r="A25">
         <v>20</v>
       </c>
       <c r="B25" t="s">
         <v>311</v>
       </c>
-      <c r="C25" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="26" ht="16.5" spans="1:3">
+      <c r="C25" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" ht="16.5" hidden="1" spans="1:3">
       <c r="A26">
         <v>21</v>
       </c>
       <c r="B26" t="s">
         <v>312</v>
       </c>
-      <c r="C26" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="27" ht="16.5" spans="1:3">
+      <c r="C26" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27" ht="16.5" hidden="1" spans="1:3">
       <c r="A27">
         <v>22</v>
       </c>
       <c r="B27" t="s">
         <v>313</v>
       </c>
-      <c r="C27" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="28" ht="16.5" spans="1:3">
+      <c r="C27" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28" ht="16.5" hidden="1" spans="1:3">
       <c r="A28">
         <v>23</v>
       </c>
       <c r="B28" t="s">
         <v>314</v>
       </c>
-      <c r="C28" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="29" ht="16.5" spans="1:3">
+      <c r="C28" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="29" ht="16.5" hidden="1" spans="1:3">
       <c r="A29">
         <v>24</v>
       </c>
       <c r="B29" t="s">
         <v>315</v>
       </c>
-      <c r="C29" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="30" ht="16.5" spans="1:3">
+      <c r="C29" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="30" ht="16.5" hidden="1" spans="1:3">
       <c r="A30">
         <v>25</v>
       </c>
       <c r="B30" t="s">
         <v>316</v>
       </c>
-      <c r="C30" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="31" ht="16.5" spans="1:3">
+      <c r="C30" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="31" ht="16.5" hidden="1" spans="1:3">
       <c r="A31">
         <v>26</v>
       </c>
       <c r="B31" t="s">
         <v>317</v>
       </c>
-      <c r="C31" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="32" ht="16.5" spans="1:3">
+      <c r="C31" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="32" ht="16.5" hidden="1" spans="1:3">
       <c r="A32">
         <v>27</v>
       </c>
       <c r="B32" t="s">
         <v>318</v>
       </c>
-      <c r="C32" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="33" ht="16.5" spans="1:3">
+      <c r="C32" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="33" ht="16.5" hidden="1" spans="1:3">
       <c r="A33">
         <v>28</v>
       </c>
       <c r="B33" t="s">
         <v>319</v>
       </c>
-      <c r="C33" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="34" ht="16.5" spans="1:3">
+      <c r="C33" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="34" ht="16.5" hidden="1" spans="1:3">
       <c r="A34">
         <v>29</v>
       </c>
       <c r="B34" t="s">
         <v>320</v>
       </c>
-      <c r="C34" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="35" ht="16.5" spans="1:3">
+      <c r="C34" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="35" ht="16.5" hidden="1" spans="1:3">
       <c r="A35">
         <v>30</v>
       </c>
       <c r="B35" t="s">
         <v>321</v>
       </c>
-      <c r="C35" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="36" ht="16.5" spans="1:3">
+      <c r="C35" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="36" ht="16.5" hidden="1" spans="1:3">
       <c r="A36">
         <v>31</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="C36" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="37" ht="16.5" spans="1:3">
+      <c r="C36" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="37" ht="16.5" hidden="1" spans="1:3">
       <c r="A37">
         <v>32</v>
       </c>
       <c r="B37" t="s">
         <v>323</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C37" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -13663,7 +13664,9 @@
       <c r="B38" t="s">
         <v>324</v>
       </c>
-      <c r="C38" s="7"/>
+      <c r="C38" s="8" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="39" ht="16.5" spans="1:3">
       <c r="A39">
@@ -13672,7 +13675,9 @@
       <c r="B39" t="s">
         <v>325</v>
       </c>
-      <c r="C39" s="7"/>
+      <c r="C39" s="8" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="40" ht="16.5" spans="1:3">
       <c r="A40">
@@ -13681,269 +13686,271 @@
       <c r="B40" t="s">
         <v>326</v>
       </c>
-      <c r="C40" s="7"/>
-    </row>
-    <row r="41" ht="16.5" spans="1:3">
+      <c r="C40" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="41" ht="16.5" hidden="1" spans="1:3">
       <c r="A41">
         <v>36</v>
       </c>
       <c r="B41" t="s">
         <v>327</v>
       </c>
-      <c r="C41" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="42" ht="16.5" spans="1:3">
+      <c r="C41" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="42" ht="16.5" hidden="1" spans="1:3">
       <c r="A42">
         <v>37</v>
       </c>
       <c r="B42" t="s">
         <v>328</v>
       </c>
-      <c r="C42" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="43" ht="16.5" spans="1:3">
+      <c r="C42" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="43" ht="16.5" hidden="1" spans="1:3">
       <c r="A43">
         <v>38</v>
       </c>
       <c r="B43" t="s">
         <v>329</v>
       </c>
-      <c r="C43" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="44" ht="16.5" spans="1:3">
+      <c r="C43" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="44" ht="16.5" hidden="1" spans="1:3">
       <c r="A44">
         <v>39</v>
       </c>
       <c r="B44" t="s">
         <v>330</v>
       </c>
-      <c r="C44" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="45" ht="16.5" spans="1:3">
+      <c r="C44" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="45" ht="16.5" hidden="1" spans="1:3">
       <c r="A45">
         <v>40</v>
       </c>
       <c r="B45" t="s">
         <v>331</v>
       </c>
-      <c r="C45" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="46" ht="16.5" spans="1:3">
+      <c r="C45" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="46" ht="16.5" hidden="1" spans="1:3">
       <c r="A46">
         <v>41</v>
       </c>
       <c r="B46" t="s">
         <v>332</v>
       </c>
-      <c r="C46" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="47" ht="16.5" spans="1:3">
+      <c r="C46" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="47" ht="16.5" hidden="1" spans="1:3">
       <c r="A47">
         <v>42</v>
       </c>
       <c r="B47" t="s">
         <v>333</v>
       </c>
-      <c r="C47" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="48" ht="16.5" spans="1:3">
+      <c r="C47" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" ht="16.5" hidden="1" spans="1:3">
       <c r="A48">
         <v>43</v>
       </c>
       <c r="B48" t="s">
         <v>334</v>
       </c>
-      <c r="C48" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="49" ht="16.5" spans="1:3">
+      <c r="C48" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49" ht="16.5" hidden="1" spans="1:3">
       <c r="A49">
         <v>44</v>
       </c>
       <c r="B49" t="s">
         <v>335</v>
       </c>
-      <c r="C49" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="50" ht="16.5" spans="1:3">
+      <c r="C49" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="50" ht="16.5" hidden="1" spans="1:3">
       <c r="A50">
         <v>45</v>
       </c>
       <c r="B50" t="s">
         <v>336</v>
       </c>
-      <c r="C50" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="51" ht="16.5" spans="1:3">
+      <c r="C50" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="51" ht="16.5" hidden="1" spans="1:3">
       <c r="A51">
         <v>46</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="C51" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="52" ht="16.5" spans="1:3">
+      <c r="C51" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="52" ht="16.5" hidden="1" spans="1:3">
       <c r="A52">
         <v>47</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="C52" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="53" ht="16.5" spans="1:3">
+      <c r="C52" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="53" ht="16.5" hidden="1" spans="1:3">
       <c r="A53">
         <v>48</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="C53" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="54" ht="16.5" spans="1:3">
+      <c r="C53" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="54" ht="16.5" hidden="1" spans="1:3">
       <c r="A54">
         <v>49</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="C54" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="55" ht="16.5" spans="1:3">
+      <c r="C54" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="55" ht="16.5" hidden="1" spans="1:3">
       <c r="A55">
         <v>50</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="C55" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="56" ht="16.5" spans="1:3">
+      <c r="C55" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="56" ht="16.5" hidden="1" spans="1:3">
       <c r="A56">
         <v>51</v>
       </c>
       <c r="B56" t="s">
         <v>342</v>
       </c>
-      <c r="C56" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="57" ht="16.5" spans="1:3">
+      <c r="C56" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="57" ht="16.5" hidden="1" spans="1:3">
       <c r="A57">
         <v>52</v>
       </c>
       <c r="B57" t="s">
         <v>343</v>
       </c>
-      <c r="C57" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="58" ht="16.5" spans="1:3">
+      <c r="C57" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="58" ht="16.5" hidden="1" spans="1:3">
       <c r="A58">
         <v>53</v>
       </c>
       <c r="B58" t="s">
         <v>344</v>
       </c>
-      <c r="C58" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="59" ht="16.5" spans="1:3">
+      <c r="C58" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="59" ht="16.5" hidden="1" spans="1:3">
       <c r="A59">
         <v>54</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="C59" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="60" ht="16.5" spans="1:3">
+      <c r="C59" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="60" ht="16.5" hidden="1" spans="1:3">
       <c r="A60">
         <v>55</v>
       </c>
       <c r="B60" t="s">
         <v>346</v>
       </c>
-      <c r="C60" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="61" ht="16.5" spans="1:3">
+      <c r="C60" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="61" ht="16.5" hidden="1" spans="1:3">
       <c r="A61">
         <v>56</v>
       </c>
       <c r="B61" t="s">
         <v>347</v>
       </c>
-      <c r="C61" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="62" ht="16.5" spans="1:3">
+      <c r="C61" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="62" ht="16.5" hidden="1" spans="1:3">
       <c r="A62">
         <v>57</v>
       </c>
       <c r="B62" t="s">
         <v>348</v>
       </c>
-      <c r="C62" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="63" ht="16.5" spans="1:3">
+      <c r="C62" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="63" ht="16.5" hidden="1" spans="1:3">
       <c r="A63">
         <v>58</v>
       </c>
       <c r="B63" t="s">
         <v>349</v>
       </c>
-      <c r="C63" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="64" ht="16.5" spans="1:3">
+      <c r="C63" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="64" ht="16.5" hidden="1" spans="1:3">
       <c r="A64">
         <v>59</v>
       </c>
       <c r="B64" t="s">
         <v>350</v>
       </c>
-      <c r="C64" s="7" t="s">
+      <c r="C64" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -13954,7 +13961,9 @@
       <c r="B65" s="5" t="s">
         <v>351</v>
       </c>
-      <c r="C65" s="7"/>
+      <c r="C65" s="8" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="66" ht="16.5" spans="1:3">
       <c r="A66">
@@ -13963,7 +13972,9 @@
       <c r="B66" s="5" t="s">
         <v>352</v>
       </c>
-      <c r="C66" s="7"/>
+      <c r="C66" s="8" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="67" ht="16.5" spans="1:3">
       <c r="A67">
@@ -13972,7 +13983,9 @@
       <c r="B67" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="C67" s="7"/>
+      <c r="C67" s="8" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="68" ht="16.5" spans="1:3">
       <c r="A68">
@@ -13981,236 +13994,238 @@
       <c r="B68" s="5" t="s">
         <v>354</v>
       </c>
-      <c r="C68" s="7"/>
-    </row>
-    <row r="69" ht="16.5" spans="1:3">
+      <c r="C68" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="69" ht="16.5" hidden="1" spans="1:3">
       <c r="A69">
         <v>64</v>
       </c>
       <c r="B69" t="s">
         <v>96</v>
       </c>
-      <c r="C69" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="70" ht="16.5" spans="1:3">
+      <c r="C69" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="70" ht="16.5" hidden="1" spans="1:3">
       <c r="A70">
         <v>65</v>
       </c>
       <c r="B70" t="s">
         <v>97</v>
       </c>
-      <c r="C70" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="71" ht="16.5" spans="1:3">
+      <c r="C70" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="71" ht="16.5" hidden="1" spans="1:3">
       <c r="A71">
         <v>66</v>
       </c>
       <c r="B71" t="s">
         <v>98</v>
       </c>
-      <c r="C71" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="72" ht="16.5" spans="1:3">
+      <c r="C71" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="72" ht="16.5" hidden="1" spans="1:3">
       <c r="A72">
         <v>67</v>
       </c>
       <c r="B72" t="s">
         <v>99</v>
       </c>
-      <c r="C72" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="73" ht="16.5" spans="1:3">
+      <c r="C72" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="73" ht="16.5" hidden="1" spans="1:3">
       <c r="A73">
         <v>68</v>
       </c>
       <c r="B73" t="s">
         <v>100</v>
       </c>
-      <c r="C73" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="74" ht="16.5" spans="1:3">
+      <c r="C73" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="74" ht="16.5" hidden="1" spans="1:3">
       <c r="A74">
         <v>69</v>
       </c>
       <c r="B74" t="s">
         <v>101</v>
       </c>
-      <c r="C74" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="75" ht="16.5" spans="1:3">
+      <c r="C74" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="75" ht="16.5" hidden="1" spans="1:3">
       <c r="A75">
         <v>70</v>
       </c>
       <c r="B75" t="s">
         <v>109</v>
       </c>
-      <c r="C75" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="76" ht="16.5" spans="1:3">
+      <c r="C75" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="76" ht="16.5" hidden="1" spans="1:3">
       <c r="A76">
         <v>71</v>
       </c>
       <c r="B76" t="s">
         <v>110</v>
       </c>
-      <c r="C76" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="77" ht="16.5" spans="1:3">
+      <c r="C76" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="77" ht="16.5" hidden="1" spans="1:3">
       <c r="A77">
         <v>72</v>
       </c>
       <c r="B77" t="s">
         <v>111</v>
       </c>
-      <c r="C77" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="78" ht="16.5" spans="1:3">
+      <c r="C77" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="78" ht="16.5" hidden="1" spans="1:3">
       <c r="A78">
         <v>73</v>
       </c>
       <c r="B78" t="s">
         <v>113</v>
       </c>
-      <c r="C78" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="79" ht="16.5" spans="1:3">
+      <c r="C78" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="79" ht="16.5" hidden="1" spans="1:3">
       <c r="A79">
         <v>74</v>
       </c>
       <c r="B79" t="s">
         <v>114</v>
       </c>
-      <c r="C79" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="80" ht="16.5" spans="1:3">
+      <c r="C79" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="80" ht="16.5" hidden="1" spans="1:3">
       <c r="A80">
         <v>75</v>
       </c>
       <c r="B80" t="s">
         <v>115</v>
       </c>
-      <c r="C80" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="81" ht="16.5" spans="1:3">
+      <c r="C80" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="81" ht="16.5" hidden="1" spans="1:3">
       <c r="A81">
         <v>76</v>
       </c>
       <c r="B81" t="s">
         <v>116</v>
       </c>
-      <c r="C81" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="82" ht="16.5" spans="1:3">
+      <c r="C81" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="82" ht="16.5" hidden="1" spans="1:3">
       <c r="A82">
         <v>77</v>
       </c>
       <c r="B82" t="s">
         <v>117</v>
       </c>
-      <c r="C82" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="83" ht="16.5" spans="1:3">
+      <c r="C82" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="83" ht="16.5" hidden="1" spans="1:3">
       <c r="A83">
         <v>78</v>
       </c>
       <c r="B83" t="s">
         <v>118</v>
       </c>
-      <c r="C83" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="84" ht="16.5" spans="1:3">
+      <c r="C83" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="84" ht="16.5" hidden="1" spans="1:3">
       <c r="A84">
         <v>79</v>
       </c>
       <c r="B84" t="s">
         <v>119</v>
       </c>
-      <c r="C84" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="85" ht="16.5" spans="1:3">
+      <c r="C84" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="85" ht="16.5" hidden="1" spans="1:3">
       <c r="A85">
         <v>80</v>
       </c>
       <c r="B85" t="s">
         <v>120</v>
       </c>
-      <c r="C85" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="86" ht="16.5" spans="1:3">
+      <c r="C85" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="86" ht="16.5" hidden="1" spans="1:3">
       <c r="A86">
         <v>81</v>
       </c>
       <c r="B86" t="s">
         <v>121</v>
       </c>
-      <c r="C86" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="87" ht="16.5" spans="1:3">
+      <c r="C86" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="87" ht="16.5" hidden="1" spans="1:3">
       <c r="A87">
         <v>82</v>
       </c>
       <c r="B87" t="s">
         <v>122</v>
       </c>
-      <c r="C87" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="88" ht="16.5" spans="1:3">
+      <c r="C87" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="88" ht="16.5" hidden="1" spans="1:3">
       <c r="A88">
         <v>83</v>
       </c>
       <c r="B88" t="s">
         <v>123</v>
       </c>
-      <c r="C88" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="89" ht="16.5" spans="1:3">
+      <c r="C88" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="89" ht="16.5" hidden="1" spans="1:3">
       <c r="A89">
         <v>84</v>
       </c>
       <c r="B89" t="s">
         <v>355</v>
       </c>
-      <c r="C89" s="7" t="s">
+      <c r="C89" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -14219,7 +14234,7 @@
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C50 C51 C52 C6:C49 C53:C54 C55:C89">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C38 C50 C51 C52 C6:C37 C39:C40 C41:C49 C53:C54 C55:C64 C65:C66 C67:C89">
       <formula1>"〇,✕"</formula1>
     </dataValidation>
   </dataValidations>
@@ -14258,7 +14273,7 @@
       </c>
       <c r="B2">
         <f>COUNTIF(表6_91213[完成情况],"〇")</f>
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -14267,7 +14282,7 @@
       </c>
       <c r="B3">
         <f>COUNTIF(表6_91213[完成情况],"✕")+COUNTIF(表6_91213[完成情况],"")</f>
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -14276,7 +14291,7 @@
       </c>
       <c r="B4" s="3">
         <f>B2/MAX(表6_91213[编号])</f>
-        <v>0.789473684210526</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -14297,7 +14312,7 @@
       <c r="B6" t="s">
         <v>356</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -14308,7 +14323,7 @@
       <c r="B7" t="s">
         <v>357</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -14319,7 +14334,7 @@
       <c r="B8" t="s">
         <v>358</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -14330,7 +14345,7 @@
       <c r="B9" t="s">
         <v>359</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -14341,7 +14356,7 @@
       <c r="B10" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -14352,7 +14367,9 @@
       <c r="B11" t="s">
         <v>361</v>
       </c>
-      <c r="C11" s="7"/>
+      <c r="C11" s="8" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="12" ht="16.5" spans="1:3">
       <c r="A12">
@@ -14361,7 +14378,7 @@
       <c r="B12" t="s">
         <v>362</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -14372,7 +14389,7 @@
       <c r="B13" t="s">
         <v>363</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -14383,7 +14400,9 @@
       <c r="B14" t="s">
         <v>364</v>
       </c>
-      <c r="C14" s="7"/>
+      <c r="C14" s="8" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="15" ht="16.5" spans="1:3">
       <c r="A15">
@@ -14392,7 +14411,9 @@
       <c r="B15" t="s">
         <v>365</v>
       </c>
-      <c r="C15" s="7"/>
+      <c r="C15" s="8" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="16" ht="16.5" spans="1:3">
       <c r="A16">
@@ -14401,7 +14422,9 @@
       <c r="B16" t="s">
         <v>366</v>
       </c>
-      <c r="C16" s="7"/>
+      <c r="C16" s="8" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="17" ht="16.5" spans="1:3">
       <c r="A17">
@@ -14410,7 +14433,7 @@
       <c r="B17" t="s">
         <v>275</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -14421,7 +14444,7 @@
       <c r="B18" t="s">
         <v>276</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -14432,7 +14455,7 @@
       <c r="B19" t="s">
         <v>279</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -14443,7 +14466,7 @@
       <c r="B20" t="s">
         <v>137</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -14454,7 +14477,7 @@
       <c r="B21" t="s">
         <v>138</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -14465,7 +14488,7 @@
       <c r="B22" t="s">
         <v>367</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -14476,7 +14499,7 @@
       <c r="B23" t="s">
         <v>368</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -14487,7 +14510,7 @@
       <c r="B24" t="s">
         <v>369</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -14496,7 +14519,7 @@
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6:C24">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C12 C13 C6:C9 C10:C11 C14:C15 C16:C24">
       <formula1>"〇,✕"</formula1>
     </dataValidation>
   </dataValidations>
@@ -14514,11 +14537,11 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<DataMashup xmlns="http://schemas.microsoft.com/DataMashup">AAAAAAQFAABQSwMECgAAAAAAh07iQAAAAAAAAAAAAAAAAAcAAABDb25maWcvUEsDBBQAAAAIAIdO4kASOP6YnwAAAPMAAAASAAAAQ29uZmlnL1BhY2thZ2UueG1shY9NC4IwHMa/iuzuNmdRyN958JoRBNF1zDVHOsPNJn36jDK6dXtefofngWLq2uiuBmd6m6MEUxQpK/vaWJ2j0V/iLSo4HIS8Cq2iGbYum1ydo8b7W0ZICAGHFPeDJozShJyr3VE2qhPoC5v/cGys88JKhTic3mM4w8lqg9N1iimQJYTK2EUzzOa9r/YnhHJs/Tgo/mjicg9ksUA+H/gTUEsDBAoAAAAAAIdO4kAAAAAAAAAAAAAAAAAJAAAARm9ybXVsYXMvUEsDBBQAAAAIAIdO4kC93Sq2pgEAAO8DAAATAAAARm9ybXVsYXMvU2VjdGlvbjEubY2SbUvCQADH3wt+h2O9WXBISxNKetUDBeELDXozCK2DhnMLN0OIIFwP68Ey0KTe1KAnKKzeiG31abbb9Ft0ZZY4XR6M42D3+//ufyehFZkTBRBvzUzE7/P7pLVEBq2CIcrMv5vKiamcm8qTmb8xlYPpmWXLMPCh5lQ1p7gHQI6XchSYBDyS/T5Ahq0XyXImt4L4wJKYSSVFMUXPcjwKTImCjARZoqm5CdZ5KjWqLyz58EfZ0nWndMWOMHa9bqundslwyrcsfs9j/c56O8Kqwv6rEgh8qwxDIGR5HgI5k0XDsOWE1evmxY1zuYP1clN5aGjHRHExkSRSMZQWN9BCQpKjNFGH4+49aqXr7ymRz6YFiXZj4SYVTaQRteWmtJOZLlgr+g+lViDj3r1bs4xz3GESRzy5sv4mDFGZl1H6T6W5X8BnH7hY+OqhgxRDAlF2k9qRcPOHBAFlv+7b24ZV327cq9SW+5RNreY8Pnf2G09x63RXdK8DtusZ9a7nN8CLEfRm/D6CUS9IaEBI0AsyNiAkBJkel97uJDwgZYyo+H2c0O/RhyOfUEsDBBQAAAAIAIdO4kB/v9PKnQAAAOQAAAATAAAAW0NvbnRlbnRfVHlwZXNdLnhtbG2PSw7CMAxErxJ5n7qwQAg17aJwAy4QBfcjmo8aF4Xbk9AdYunxPM+46ZJdxIvWOHun4FDVIMgZ/5jdqGDjQZ6ha5v7O1AU2eqigok5XBCjmcjqWPlALm8Gv1rNeVxHDNo89Uh4rOsTGu+YHEsuN6BtrjTobWFxS1neYzMOot99JUoBU2IsMv4F7I9dh7DMRnN+ApO0UdoC4rd2+wFQSwECFAAUAAAACACHTuJAf7/Typ0AAADkAAAAEwAAAAAAAAABACAAAADyAgAAW0NvbnRlbnRfVHlwZXNdLnhtbFBLAQIUAAoAAAAAAIdO4kAAAAAAAAAAAAAAAAAHAAAAAAAAAAAAEAAAAAAAAABDb25maWcvUEsBAhQAFAAAAAgAh07iQBI4/pifAAAA8wAAABIAAAAAAAAAAQAgAAAAJQAAAENvbmZpZy9QYWNrYWdlLnhtbFBLAQIUAAoAAAAAAIdO4kAAAAAAAAAAAAAAAAAJAAAAAAAAAAAAEAAAAPQAAABGb3JtdWxhcy9QSwECFAAUAAAACACHTuJAvd0qtqYBAADvAwAAEwAAAAAAAAABACAAAAAbAQAARm9ybXVsYXMvU2VjdGlvbjEubVBLBQYAAAAABQAFAC4BAADAAwAAAAAOAQAAPD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXRmLTgiID8+PFBlcm1pc3Npb25MaXN0IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiPjxDYW5FdmFsdWF0ZUZ1dHVyZVBhY2thZ2VzPmZhbHNlPC9DYW5FdmFsdWF0ZUZ1dHVyZVBhY2thZ2VzPjxGaXJld2FsbEVuYWJsZWQ+dHJ1ZTwvRmlyZXdhbGxFbmFibGVkPjwvUGVybWlzc2lvbkxpc3Q+kwQAAAAAAABxBAAAPD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXRmLTgiID8+PExvY2FsUGFja2FnZU1ldGFkYXRhRmlsZSB4bWxuczp4c2Q9Imh0dHA6Ly93d3cudzMub3JnLzIwMDEvWE1MU2NoZW1hIiB4bWxuczp4c2k9Imh0dHA6Ly93d3cudzMub3JnLzIwMDEvWE1MU2NoZW1hLWluc3RhbmNlIj48SXRlbXM+PEl0ZW0+PEl0ZW1Mb2NhdGlvbj48SXRlbVR5cGU+QWxsRm9ybXVsYXM8L0l0ZW1UeXBlPjxJdGVtUGF0aCAvPjwvSXRlbUxvY2F0aW9uPjxTdGFibGVFbnRyaWVzPjxFbnRyeSBUeXBlPSJSZWxhdGlvbnNoaXBzIiBWYWx1ZT0ic0FBQUFBQT09IiAvPjwvU3RhYmxlRW50cmllcz48L0l0ZW0+PEl0ZW0+PEl0ZW1Mb2NhdGlvbj48SXRlbVR5cGU+Rm9ybXVsYTwvSXRlbVR5cGU+PEl0ZW1QYXRoPlNlY3Rpb24xLyVFMyU4MiVCQyVFMyU4MyU4RSVFMyU4MyU5NiVFMyU4MyVBQyVFMyU4MiVBNCVFMyU4MyU4OURFXyVFNCVCQiVCQiVFNSU4QSVBMSVFNyVBRSVBMSVFNyU5MCU4NiUyMCUyMHhsc3g8L0l0ZW1QYXRoPjwvSXRlbUxvY2F0aW9uPjxTdGFibGVFbnRyaWVzPjxFbnRyeSBUeXBlPSJJc1ByaXZhdGUiIFZhbHVlPSJsMCIgLz48RW50cnkgVHlwZT0iRmlsbEVuYWJsZWQiIFZhbHVlPSJsMSIgLz48RW50cnkgVHlwZT0iRmlsbE9iamVjdFR5cGUiIFZhbHVlPSJzVGFibGUiIC8+PEVudHJ5IFR5cGU9IlF1ZXJ5SUQiIFZhbHVlPSJzMzI0MDk1OTItMTBmMi00ZDk4LWI0OWQtNDlmNmQzYmIxMDAwIiAvPjxFbnRyeSBUeXBlPSJSZXN1bHRUeXBlIiBWYWx1ZT0ic1RhYmxlIiAvPjxFbnRyeSBUeXBlPSJGaWxsVGFyZ2V0IiBWYWx1ZT0ic+ihqF/jgrzjg47jg5bjg6zjgqTjg4lERV/ku7vliqHnrqHnkIZfX3hsc3giIC8+PEVudHJ5IFR5cGU9IkZpbGxDb3VudCIgVmFsdWU9ImwxNyIgLz48RW50cnkgVHlwZT0iRmlsbEVycm9yQ291bnQiIFZhbHVlPSJsMCIgLz48RW50cnkgVHlwZT0iRmlsbExhc3RVcGRhdGVkIiBWYWx1ZT0iZDIwMjYtMDUtMDZUMDU6MjE6MDMuNzY3MDAwMFoiIC8+PEVudHJ5IFR5cGU9IkZpbGxDb2x1bW5OYW1lcyIgVmFsdWU9J3NbJnF1b3Q75rGH5oC75LiA6KeIJnF1b3Q7XScgLz48L1N0YWJsZUVudHJpZXM+PC9JdGVtPjwvSXRlbXM+PC9Mb2NhbFBhY2thZ2VNZXRhZGF0YUZpbGU+FgAAAFBLBQYAAAAAAAAAAAAAAAAAAAAAAAAmAQAAAQAAANCMnd8BFdERjHoAwE/Cl+sBAAAA2cHvIhDB8U+DzvEXf4lk6wAAAAACAAAAAAAQZgAAAAEAACAAAAA8EpwDew2CDIUHW9ZgW/1ivK7bcOsRbu/0dTKCsyDKVQAAAAAOgAAAAAIAACAAAADw1c03kaCuNh2rscf2W7gcS8HVT5kX8OAabXguH3ZdzFAAAAD8+pPMzsPq2NyQPxxQPYekie7p1wlZI7QT2iitgNCb2E+8vmLv8/T4BdRuNuPEc024N7R9QPHeFZgwT6Va4N6jL9EN5EsINmOXTEmlOrrv20AAAADVyCmBuUhQ41WsUNSSUrPwREsPXRMXnFjZiBGb6tjMquyVC8luxc8zj0emh0OXNJevy+iEBzPq7r2uMgb27P+h</DataMashup>
+<DataMashup xmlns="http://schemas.microsoft.com/DataMashup">AAAAAAQFAABQSwMECgAAAAAAh07iQAAAAAAAAAAAAAAAAAcAAABDb25maWcvUEsDBBQAAAAIAIdO4kASOP6YnwAAAPMAAAASAAAAQ29uZmlnL1BhY2thZ2UueG1shY9NC4IwHMa/iuzuNmdRyN958JoRBNF1zDVHOsPNJn36jDK6dXtefofngWLq2uiuBmd6m6MEUxQpK/vaWJ2j0V/iLSo4HIS8Cq2iGbYum1ydo8b7W0ZICAGHFPeDJozShJyr3VE2qhPoC5v/cGys88JKhTic3mM4w8lqg9N1iimQJYTK2EUzzOa9r/YnhHJs/Tgo/mjicg9ksUA+H/gTUEsDBAoAAAAAAIdO4kAAAAAAAAAAAAAAAAAJAAAARm9ybXVsYXMvUEsDBBQAAAAIAIdO4kC93Sq2pgEAAO8DAAATAAAARm9ybXVsYXMvU2VjdGlvbjEubY2SbUvCQADH3wt+h2O9WXBISxNKetUDBeELDXozCK2DhnMLN0OIIFwP68Ey0KTe1KAnKKzeiG31abbb9Ft0ZZY4XR6M42D3+//ufyehFZkTBRBvzUzE7/P7pLVEBq2CIcrMv5vKiamcm8qTmb8xlYPpmWXLMPCh5lQ1p7gHQI6XchSYBDyS/T5Ahq0XyXImt4L4wJKYSSVFMUXPcjwKTImCjARZoqm5CdZ5KjWqLyz58EfZ0nWndMWOMHa9bqundslwyrcsfs9j/c56O8Kqwv6rEgh8qwxDIGR5HgI5k0XDsOWE1evmxY1zuYP1clN5aGjHRHExkSRSMZQWN9BCQpKjNFGH4+49aqXr7ymRz6YFiXZj4SYVTaQRteWmtJOZLlgr+g+lViDj3r1bs4xz3GESRzy5sv4mDFGZl1H6T6W5X8BnH7hY+OqhgxRDAlF2k9qRcPOHBAFlv+7b24ZV327cq9SW+5RNreY8Pnf2G09x63RXdK8DtusZ9a7nN8CLEfRm/D6CUS9IaEBI0AsyNiAkBJkel97uJDwgZYyo+H2c0O/RhyOfUEsDBBQAAAAIAIdO4kB/v9PKnQAAAOQAAAATAAAAW0NvbnRlbnRfVHlwZXNdLnhtbG2PSw7CMAxErxJ5n7qwQAg17aJwAy4QBfcjmo8aF4Xbk9AdYunxPM+46ZJdxIvWOHun4FDVIMgZ/5jdqGDjQZ6ha5v7O1AU2eqigok5XBCjmcjqWPlALm8Gv1rNeVxHDNo89Uh4rOsTGu+YHEsuN6BtrjTobWFxS1neYzMOot99JUoBU2IsMv4F7I9dh7DMRnN+ApO0UdoC4rd2+wFQSwECFAAUAAAACACHTuJAf7/Typ0AAADkAAAAEwAAAAAAAAABACAAAADyAgAAW0NvbnRlbnRfVHlwZXNdLnhtbFBLAQIUAAoAAAAAAIdO4kAAAAAAAAAAAAAAAAAHAAAAAAAAAAAAEAAAAAAAAABDb25maWcvUEsBAhQAFAAAAAgAh07iQBI4/pifAAAA8wAAABIAAAAAAAAAAQAgAAAAJQAAAENvbmZpZy9QYWNrYWdlLnhtbFBLAQIUAAoAAAAAAIdO4kAAAAAAAAAAAAAAAAAJAAAAAAAAAAAAEAAAAPQAAABGb3JtdWxhcy9QSwECFAAUAAAACACHTuJAvd0qtqYBAADvAwAAEwAAAAAAAAABACAAAAAbAQAARm9ybXVsYXMvU2VjdGlvbjEubVBLBQYAAAAABQAFAC4BAADAAwAAAAAOAQAAPD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXRmLTgiID8+PFBlcm1pc3Npb25MaXN0IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiPjxDYW5FdmFsdWF0ZUZ1dHVyZVBhY2thZ2VzPmZhbHNlPC9DYW5FdmFsdWF0ZUZ1dHVyZVBhY2thZ2VzPjxGaXJld2FsbEVuYWJsZWQ+dHJ1ZTwvRmlyZXdhbGxFbmFibGVkPjwvUGVybWlzc2lvbkxpc3Q+kwQAAAAAAABxBAAAPD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXRmLTgiID8+PExvY2FsUGFja2FnZU1ldGFkYXRhRmlsZSB4bWxuczp4c2Q9Imh0dHA6Ly93d3cudzMub3JnLzIwMDEvWE1MU2NoZW1hIiB4bWxuczp4c2k9Imh0dHA6Ly93d3cudzMub3JnLzIwMDEvWE1MU2NoZW1hLWluc3RhbmNlIj48SXRlbXM+PEl0ZW0+PEl0ZW1Mb2NhdGlvbj48SXRlbVR5cGU+QWxsRm9ybXVsYXM8L0l0ZW1UeXBlPjxJdGVtUGF0aCAvPjwvSXRlbUxvY2F0aW9uPjxTdGFibGVFbnRyaWVzPjxFbnRyeSBUeXBlPSJSZWxhdGlvbnNoaXBzIiBWYWx1ZT0ic0FBQUFBQT09IiAvPjwvU3RhYmxlRW50cmllcz48L0l0ZW0+PEl0ZW0+PEl0ZW1Mb2NhdGlvbj48SXRlbVR5cGU+Rm9ybXVsYTwvSXRlbVR5cGU+PEl0ZW1QYXRoPlNlY3Rpb24xLyVFMyU4MiVCQyVFMyU4MyU4RSVFMyU4MyU5NiVFMyU4MyVBQyVFMyU4MiVBNCVFMyU4MyU4OURFXyVFNCVCQiVCQiVFNSU4QSVBMSVFNyVBRSVBMSVFNyU5MCU4NiUyMCUyMHhsc3g8L0l0ZW1QYXRoPjwvSXRlbUxvY2F0aW9uPjxTdGFibGVFbnRyaWVzPjxFbnRyeSBUeXBlPSJJc1ByaXZhdGUiIFZhbHVlPSJsMCIgLz48RW50cnkgVHlwZT0iRmlsbEVuYWJsZWQiIFZhbHVlPSJsMSIgLz48RW50cnkgVHlwZT0iRmlsbE9iamVjdFR5cGUiIFZhbHVlPSJzVGFibGUiIC8+PEVudHJ5IFR5cGU9IlF1ZXJ5SUQiIFZhbHVlPSJzMzI0MDk1OTItMTBmMi00ZDk4LWI0OWQtNDlmNmQzYmIxMDAwIiAvPjxFbnRyeSBUeXBlPSJSZXN1bHRUeXBlIiBWYWx1ZT0ic1RhYmxlIiAvPjxFbnRyeSBUeXBlPSJGaWxsVGFyZ2V0IiBWYWx1ZT0ic+ihqF/jgrzjg47jg5bjg6zjgqTjg4lERV/ku7vliqHnrqHnkIZfX3hsc3giIC8+PEVudHJ5IFR5cGU9IkZpbGxDb3VudCIgVmFsdWU9ImwxNyIgLz48RW50cnkgVHlwZT0iRmlsbEVycm9yQ291bnQiIFZhbHVlPSJsMCIgLz48RW50cnkgVHlwZT0iRmlsbExhc3RVcGRhdGVkIiBWYWx1ZT0iZDIwMjYtMDUtMDZUMDU6MjE6MDMuNzY3MDAwMFoiIC8+PEVudHJ5IFR5cGU9IkZpbGxDb2x1bW5OYW1lcyIgVmFsdWU9J3NbJnF1b3Q75rGH5oC75LiA6KeIJnF1b3Q7XScgLz48L1N0YWJsZUVudHJpZXM+PC9JdGVtPjwvSXRlbXM+PC9Mb2NhbFBhY2thZ2VNZXRhZGF0YUZpbGU+FgAAAFBLBQYAAAAAAAAAAAAAAAAAAAAAAAAmAQAAAQAAANCMnd8BFdERjHoAwE/Cl+sBAAAA2cHvIhDB8U+DzvEXf4lk6wAAAAACAAAAAAAQZgAAAAEAACAAAABF1dApCu80z6/ns3314omgTk+PiwT9BGbO8VjfPsLiFwAAAAAOgAAAAAIAACAAAAAJMWq9dqhSwS7sBLzU2/17c3qF5qb0bePBWF7rHztEP1AAAAAbHwWWgl+ErtlO2hDTXRuEX9uc0RkS18cdeT0AOcPEAFBGgrE750PTQOTa80qYYxthdAdUic5UXlTactXAaF/YUHyxskxX9dCwhAyEOW00tUAAAAC+DILDxywQkdDTOsU7hjJS8+1ebycbZS6wosjpQTXKHfouIHgg5J0dMeusZ7dEzM6zAkobtbPfOcpz51c4MNnD</DataMashup>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58AB6B07-D633-4F13-A540-283D7159BD8D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5378D2E8-D69E-404B-8989-C9B712A994BE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/DataMashup"/>
   </ds:schemaRefs>
